--- a/G_arbol_expansion_minima/graficas.xlsx
+++ b/G_arbol_expansion_minima/graficas.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\arbol_expansion_minima\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\G_arbol_expansion_minima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A902E94-E46B-43C8-8D32-41F557E7D078}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF57A62-DA35-407D-92A1-F69D448618AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1695" yWindow="1590" windowWidth="22020" windowHeight="12825" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -25,6 +25,14 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>kruscal</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -91,15 +99,58 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10553701461093383"/>
+          <c:y val="9.2788689246200692E-2"/>
+          <c:w val="0.71601772971261202"/>
+          <c:h val="0.72807545585104017"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:v>Prim</c:v>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -124,7 +175,616 @@
               <a:effectLst/>
             </c:spPr>
           </c:marker>
-          <c:val>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$B$3:$B$202</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="200"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>275</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>325</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>345</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>355</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>395</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>405</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>415</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>425</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>435</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>465</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>475</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>485</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>495</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>505</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>525</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>545</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>555</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>565</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>575</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>585</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>595</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>610</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>635</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>645</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>655</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>665</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>685</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>695</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>705</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>715</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>735</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>745</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>755</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>765</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>775</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>785</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>805</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>815</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>835</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>845</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>855</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>865</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>885</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>895</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>905</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>915</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>925</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>935</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>945</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>955</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>965</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>985</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>995</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
             <c:numRef>
               <c:f>Hoja1!$C$3:$C$202</c:f>
               <c:numCache>
@@ -732,11 +1392,11 @@
                 </c:pt>
               </c:numCache>
             </c:numRef>
-          </c:val>
+          </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-DA88-4605-B4A5-3F3A7F96806D}"/>
+              <c16:uniqueId val="{00000001-E235-407C-90F5-259EFDF30DEE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -748,18 +1408,72 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
         <c:axId val="479156384"/>
         <c:axId val="484174448"/>
-      </c:lineChart>
-      <c:catAx>
+      </c:scatterChart>
+      <c:valAx>
         <c:axId val="479156384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>N</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -798,11 +1512,8 @@
         </c:txPr>
         <c:crossAx val="484174448"/>
         <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
       <c:valAx>
         <c:axId val="484174448"/>
         <c:scaling>
@@ -824,6 +1535,61 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>Tiempos</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -857,7 +1623,7 @@
         </c:txPr>
         <c:crossAx val="479156384"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -867,6 +1633,750 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="es-MX"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Kruskal(ms)</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Hoja1!$J$29:$J$78</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>110</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>130</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>150</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>170</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>190</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>210</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>230</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>250</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>270</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>290</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>310</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>330</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>350</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>390</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>410</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>430</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>450</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>470</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>510</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>530</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>550</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>570</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>590</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>610</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>630</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>650</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>670</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>690</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>710</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>730</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>750</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>770</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>790</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>830</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>890</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>910</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>930</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>950</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>970</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>990</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Hoja1!$K$29:$K$78</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="50"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.107143</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7.1429000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>7.1429000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.214286</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>7.1429000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7.1429000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.107143</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.17857100000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.32142900000000002</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.28571400000000002</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.35714299999999999</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.32142900000000002</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.57142899999999996</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.46428599999999998</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.53571400000000002</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>0.39285700000000001</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>0.57142899999999996</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>0.42857099999999998</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>0.57142899999999996</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>0.71428599999999998</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>0.82142899999999996</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>0.96428599999999998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>0.89285700000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>0.96428599999999998</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>0.96428599999999998</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1.035714</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1.071429</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1.071429</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1.214286</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>1.321429</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1.357143</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1.428571</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1.464286</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1.785714</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1.714286</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1.892857</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>1.857143</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2.0714290000000002</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2.1071430000000002</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FC1B-43F9-902D-DF59506D16F9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="479156384"/>
+        <c:axId val="484174448"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="479156384"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>N</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="484174448"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="484174448"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="es-MX"/>
+                  <a:t>Tiempos</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="es-MX"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="479156384"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:extLst>
@@ -951,6 +2461,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
@@ -1454,20 +3004,523 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>561974</xdr:colOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>272414</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>52387</xdr:rowOff>
+      <xdr:rowOff>82867</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>495299</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>472440</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1487,6 +3540,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>205740</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{668DB9A0-AA34-4DC9-A24A-A7B47BC7743D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1758,10 +3849,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:C202"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B3:K202"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>5</v>
       </c>
@@ -1769,7 +3860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>10</v>
       </c>
@@ -1777,7 +3868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>15</v>
       </c>
@@ -1785,7 +3876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>20</v>
       </c>
@@ -1793,7 +3884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>25</v>
       </c>
@@ -1801,7 +3892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>30</v>
       </c>
@@ -1809,7 +3900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>35</v>
       </c>
@@ -1817,7 +3908,7 @@
         <v>3.6000000000000001E-5</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>40</v>
       </c>
@@ -1825,7 +3916,7 @@
         <v>7.1000000000000005E-5</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>45</v>
       </c>
@@ -1833,7 +3924,7 @@
         <v>7.1000000000000005E-5</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>50</v>
       </c>
@@ -1841,7 +3932,7 @@
         <v>1.4300000000000001E-4</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>55</v>
       </c>
@@ -1849,7 +3940,7 @@
         <v>1.07E-4</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>60</v>
       </c>
@@ -1857,7 +3948,7 @@
         <v>1.7899999999999999E-4</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>65</v>
       </c>
@@ -1865,7 +3956,7 @@
         <v>2.5000000000000001E-4</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>70</v>
       </c>
@@ -1873,7 +3964,7 @@
         <v>1.7899999999999999E-4</v>
       </c>
     </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>75</v>
       </c>
@@ -1881,7 +3972,7 @@
         <v>1.7899999999999999E-4</v>
       </c>
     </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>80</v>
       </c>
@@ -1889,7 +3980,7 @@
         <v>4.2900000000000002E-4</v>
       </c>
     </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>85</v>
       </c>
@@ -1897,7 +3988,7 @@
         <v>3.21E-4</v>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>90</v>
       </c>
@@ -1905,7 +3996,7 @@
         <v>5.0000000000000001E-4</v>
       </c>
     </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>95</v>
       </c>
@@ -1913,7 +4004,7 @@
         <v>3.9300000000000001E-4</v>
       </c>
     </row>
-    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>100</v>
       </c>
@@ -1921,7 +4012,7 @@
         <v>6.7900000000000002E-4</v>
       </c>
     </row>
-    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>105</v>
       </c>
@@ -1929,7 +4020,7 @@
         <v>7.8600000000000002E-4</v>
       </c>
     </row>
-    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>110</v>
       </c>
@@ -1937,7 +4028,7 @@
         <v>8.9300000000000002E-4</v>
       </c>
     </row>
-    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>115</v>
       </c>
@@ -1945,7 +4036,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>120</v>
       </c>
@@ -1953,7 +4044,7 @@
         <v>1.0709999999999999E-3</v>
       </c>
     </row>
-    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>125</v>
       </c>
@@ -1961,415 +4052,718 @@
         <v>1.25E-3</v>
       </c>
     </row>
-    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>130</v>
       </c>
       <c r="C28">
         <v>1.3209999999999999E-3</v>
       </c>
-    </row>
-    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J28" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>135</v>
       </c>
       <c r="C29">
         <v>1.5709999999999999E-3</v>
       </c>
-    </row>
-    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J29">
+        <v>10</v>
+      </c>
+      <c r="K29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>140</v>
       </c>
       <c r="C30">
         <v>1.786E-3</v>
       </c>
-    </row>
-    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J30">
+        <v>30</v>
+      </c>
+      <c r="K30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>145</v>
       </c>
       <c r="C31">
         <v>2E-3</v>
       </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J31">
+        <v>50</v>
+      </c>
+      <c r="K31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>150</v>
       </c>
       <c r="C32">
         <v>2.2859999999999998E-3</v>
       </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J32">
+        <v>70</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>155</v>
       </c>
       <c r="C33">
         <v>2.4290000000000002E-3</v>
       </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J33">
+        <v>90</v>
+      </c>
+      <c r="K33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>160</v>
       </c>
       <c r="C34">
         <v>2.6069999999999999E-3</v>
       </c>
-    </row>
-    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J34">
+        <v>110</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>165</v>
       </c>
       <c r="C35">
         <v>2.8570000000000002E-3</v>
       </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J35">
+        <v>130</v>
+      </c>
+      <c r="K35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>170</v>
       </c>
       <c r="C36">
         <v>3.0360000000000001E-3</v>
       </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J36">
+        <v>150</v>
+      </c>
+      <c r="K36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>175</v>
       </c>
       <c r="C37">
         <v>3.107E-3</v>
       </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J37">
+        <v>170</v>
+      </c>
+      <c r="K37">
+        <v>0.107143</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>180</v>
       </c>
       <c r="C38">
         <v>3.7859999999999999E-3</v>
       </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J38">
+        <v>190</v>
+      </c>
+      <c r="K38">
+        <v>7.1429000000000006E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>185</v>
       </c>
       <c r="C39">
         <v>4.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J39">
+        <v>210</v>
+      </c>
+      <c r="K39">
+        <v>7.1429000000000006E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>190</v>
       </c>
       <c r="C40">
         <v>4.3930000000000002E-3</v>
       </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J40">
+        <v>230</v>
+      </c>
+      <c r="K40">
+        <v>0.214286</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>195</v>
       </c>
       <c r="C41">
         <v>4.4640000000000001E-3</v>
       </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J41">
+        <v>250</v>
+      </c>
+      <c r="K41">
+        <v>7.1429000000000006E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>200</v>
       </c>
       <c r="C42">
         <v>5.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J42">
+        <v>270</v>
+      </c>
+      <c r="K42">
+        <v>7.1429000000000006E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>205</v>
       </c>
       <c r="C43">
         <v>5.4289999999999998E-3</v>
       </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J43">
+        <v>290</v>
+      </c>
+      <c r="K43">
+        <v>0.107143</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>210</v>
       </c>
       <c r="C44">
         <v>5.7860000000000003E-3</v>
       </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J44">
+        <v>310</v>
+      </c>
+      <c r="K44">
+        <v>0.17857100000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>215</v>
       </c>
       <c r="C45">
         <v>6.2139999999999999E-3</v>
       </c>
-    </row>
-    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J45">
+        <v>330</v>
+      </c>
+      <c r="K45">
+        <v>0.32142900000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>220</v>
       </c>
       <c r="C46">
         <v>6.8929999999999998E-3</v>
       </c>
-    </row>
-    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J46">
+        <v>350</v>
+      </c>
+      <c r="K46">
+        <v>0.28571400000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>225</v>
       </c>
       <c r="C47">
         <v>7.0359999999999997E-3</v>
       </c>
-    </row>
-    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J47">
+        <v>370</v>
+      </c>
+      <c r="K47">
+        <v>0.35714299999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>230</v>
       </c>
       <c r="C48">
         <v>7.4640000000000001E-3</v>
       </c>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J48">
+        <v>390</v>
+      </c>
+      <c r="K48">
+        <v>0.32142900000000002</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>235</v>
       </c>
       <c r="C49">
         <v>8.0000000000000002E-3</v>
       </c>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J49">
+        <v>410</v>
+      </c>
+      <c r="K49">
+        <v>0.57142899999999996</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>240</v>
       </c>
       <c r="C50">
         <v>8.6070000000000001E-3</v>
       </c>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J50">
+        <v>430</v>
+      </c>
+      <c r="K50">
+        <v>0.46428599999999998</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>245</v>
       </c>
       <c r="C51">
         <v>8.9999999999999993E-3</v>
       </c>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J51">
+        <v>450</v>
+      </c>
+      <c r="K51">
+        <v>0.53571400000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>250</v>
       </c>
       <c r="C52">
         <v>9.6430000000000005E-3</v>
       </c>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <v>470</v>
+      </c>
+      <c r="K52">
+        <v>0.39285700000000001</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>255</v>
       </c>
       <c r="C53">
         <v>1.0142999999999999E-2</v>
       </c>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J53">
+        <v>490</v>
+      </c>
+      <c r="K53">
+        <v>0.57142899999999996</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>260</v>
       </c>
       <c r="C54">
         <v>1.0678999999999999E-2</v>
       </c>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J54">
+        <v>510</v>
+      </c>
+      <c r="K54">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>265</v>
       </c>
       <c r="C55">
         <v>1.1285999999999999E-2</v>
       </c>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J55">
+        <v>530</v>
+      </c>
+      <c r="K55">
+        <v>0.42857099999999998</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>270</v>
       </c>
       <c r="C56">
         <v>1.1964000000000001E-2</v>
       </c>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J56">
+        <v>550</v>
+      </c>
+      <c r="K56">
+        <v>0.57142899999999996</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>275</v>
       </c>
       <c r="C57">
         <v>1.2678999999999999E-2</v>
       </c>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J57">
+        <v>570</v>
+      </c>
+      <c r="K57">
+        <v>0.71428599999999998</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>280</v>
       </c>
       <c r="C58">
         <v>1.3285999999999999E-2</v>
       </c>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J58">
+        <v>590</v>
+      </c>
+      <c r="K58">
+        <v>0.82142899999999996</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>285</v>
       </c>
       <c r="C59">
         <v>1.4071E-2</v>
       </c>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J59">
+        <v>610</v>
+      </c>
+      <c r="K59">
+        <v>0.96428599999999998</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>290</v>
       </c>
       <c r="C60">
         <v>1.4321E-2</v>
       </c>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J60">
+        <v>630</v>
+      </c>
+      <c r="K60">
+        <v>0.89285700000000001</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>295</v>
       </c>
       <c r="C61">
         <v>1.5535999999999999E-2</v>
       </c>
-    </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J61">
+        <v>650</v>
+      </c>
+      <c r="K61">
+        <v>0.96428599999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>300</v>
       </c>
       <c r="C62">
         <v>1.6463999999999999E-2</v>
       </c>
-    </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J62">
+        <v>670</v>
+      </c>
+      <c r="K62">
+        <v>0.96428599999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>305</v>
       </c>
       <c r="C63">
         <v>1.7107000000000001E-2</v>
       </c>
-    </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J63">
+        <v>690</v>
+      </c>
+      <c r="K63">
+        <v>1.035714</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>310</v>
       </c>
       <c r="C64">
         <v>1.8107000000000002E-2</v>
       </c>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J64">
+        <v>710</v>
+      </c>
+      <c r="K64">
+        <v>1.071429</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>315</v>
       </c>
       <c r="C65">
         <v>1.8643E-2</v>
       </c>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J65">
+        <v>730</v>
+      </c>
+      <c r="K65">
+        <v>1.071429</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>320</v>
       </c>
       <c r="C66">
         <v>1.9963999999999999E-2</v>
       </c>
-    </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J66">
+        <v>750</v>
+      </c>
+      <c r="K66">
+        <v>1.214286</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>325</v>
       </c>
       <c r="C67">
         <v>2.0607E-2</v>
       </c>
-    </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J67">
+        <v>770</v>
+      </c>
+      <c r="K67">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>330</v>
       </c>
       <c r="C68">
         <v>2.1714000000000001E-2</v>
       </c>
-    </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J68">
+        <v>790</v>
+      </c>
+      <c r="K68">
+        <v>1.321429</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>335</v>
       </c>
       <c r="C69">
         <v>2.2536E-2</v>
       </c>
-    </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J69">
+        <v>810</v>
+      </c>
+      <c r="K69">
+        <v>1.357143</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>340</v>
       </c>
       <c r="C70">
         <v>2.3643000000000001E-2</v>
       </c>
-    </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J70">
+        <v>830</v>
+      </c>
+      <c r="K70">
+        <v>1.428571</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>345</v>
       </c>
       <c r="C71">
         <v>2.4535999999999999E-2</v>
       </c>
-    </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J71">
+        <v>850</v>
+      </c>
+      <c r="K71">
+        <v>1.464286</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>350</v>
       </c>
       <c r="C72">
         <v>2.5786E-2</v>
       </c>
-    </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J72">
+        <v>870</v>
+      </c>
+      <c r="K72">
+        <v>1.785714</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>355</v>
       </c>
       <c r="C73">
         <v>2.6856999999999999E-2</v>
       </c>
-    </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J73">
+        <v>890</v>
+      </c>
+      <c r="K73">
+        <v>1.714286</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>360</v>
       </c>
       <c r="C74">
         <v>2.8035999999999998E-2</v>
       </c>
-    </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J74">
+        <v>910</v>
+      </c>
+      <c r="K74">
+        <v>1.892857</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>365</v>
       </c>
       <c r="C75">
         <v>2.9749999999999999E-2</v>
       </c>
-    </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J75">
+        <v>930</v>
+      </c>
+      <c r="K75">
+        <v>1.857143</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>370</v>
       </c>
       <c r="C76">
         <v>3.0321000000000001E-2</v>
       </c>
-    </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J76">
+        <v>950</v>
+      </c>
+      <c r="K76">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>375</v>
       </c>
       <c r="C77">
         <v>3.1928999999999999E-2</v>
       </c>
-    </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J77">
+        <v>970</v>
+      </c>
+      <c r="K77">
+        <v>2.0714290000000002</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>380</v>
       </c>
       <c r="C78">
         <v>3.3429E-2</v>
       </c>
-    </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="J78">
+        <v>990</v>
+      </c>
+      <c r="K78">
+        <v>2.1071430000000002</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>385</v>
       </c>
@@ -2377,7 +4771,7 @@
         <v>3.4679000000000001E-2</v>
       </c>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>390</v>
       </c>
@@ -2385,7 +4779,7 @@
         <v>3.5785999999999998E-2</v>
       </c>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>395</v>
       </c>
@@ -2393,7 +4787,7 @@
         <v>3.6679000000000003E-2</v>
       </c>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>400</v>
       </c>
@@ -2401,7 +4795,7 @@
         <v>3.8071000000000001E-2</v>
       </c>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>405</v>
       </c>
@@ -2409,7 +4803,7 @@
         <v>3.9607000000000003E-2</v>
       </c>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>410</v>
       </c>
@@ -2417,7 +4811,7 @@
         <v>4.0856999999999997E-2</v>
       </c>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>415</v>
       </c>
@@ -2425,7 +4819,7 @@
         <v>4.2606999999999999E-2</v>
       </c>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>420</v>
       </c>
@@ -2433,7 +4827,7 @@
         <v>4.4249999999999998E-2</v>
       </c>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>425</v>
       </c>
@@ -2441,7 +4835,7 @@
         <v>4.5678999999999997E-2</v>
       </c>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>430</v>
       </c>
@@ -2449,7 +4843,7 @@
         <v>4.7071000000000002E-2</v>
       </c>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>435</v>
       </c>
@@ -2457,7 +4851,7 @@
         <v>4.9070999999999997E-2</v>
       </c>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>440</v>
       </c>
@@ -2465,7 +4859,7 @@
         <v>5.0285999999999997E-2</v>
       </c>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>445</v>
       </c>
@@ -2473,7 +4867,7 @@
         <v>5.2357000000000001E-2</v>
       </c>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>450</v>
       </c>
@@ -2481,7 +4875,7 @@
         <v>5.3928999999999998E-2</v>
       </c>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>455</v>
       </c>
@@ -2489,7 +4883,7 @@
         <v>5.6000000000000001E-2</v>
       </c>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>460</v>
       </c>
@@ -2497,7 +4891,7 @@
         <v>5.7964000000000002E-2</v>
       </c>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>465</v>
       </c>
@@ -2505,7 +4899,7 @@
         <v>5.9464000000000003E-2</v>
       </c>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>470</v>
       </c>
@@ -2513,7 +4907,7 @@
         <v>6.1607000000000002E-2</v>
       </c>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>475</v>
       </c>
@@ -2521,7 +4915,7 @@
         <v>6.3535999999999995E-2</v>
       </c>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>480</v>
       </c>
@@ -2529,7 +4923,7 @@
         <v>6.5679000000000001E-2</v>
       </c>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>485</v>
       </c>
@@ -2537,7 +4931,7 @@
         <v>6.7785999999999999E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>490</v>
       </c>
@@ -2545,7 +4939,7 @@
         <v>6.9642999999999997E-2</v>
       </c>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>495</v>
       </c>
@@ -2553,7 +4947,7 @@
         <v>7.1714E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>500</v>
       </c>
@@ -2561,7 +4955,7 @@
         <v>7.5036000000000005E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>505</v>
       </c>
@@ -2569,7 +4963,7 @@
         <v>7.8E-2</v>
       </c>
     </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>510</v>
       </c>
@@ -2577,7 +4971,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>515</v>
       </c>
@@ -2585,7 +4979,7 @@
         <v>8.0679000000000001E-2</v>
       </c>
     </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>520</v>
       </c>
@@ -2593,7 +4987,7 @@
         <v>8.2392999999999994E-2</v>
       </c>
     </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>525</v>
       </c>
@@ -2601,7 +4995,7 @@
         <v>8.5142999999999996E-2</v>
       </c>
     </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>530</v>
       </c>
@@ -2609,7 +5003,7 @@
         <v>8.7320999999999996E-2</v>
       </c>
     </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>535</v>
       </c>
@@ -2617,7 +5011,7 @@
         <v>9.0428999999999995E-2</v>
       </c>
     </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>540</v>
       </c>
@@ -2625,7 +5019,7 @@
         <v>9.2964000000000005E-2</v>
       </c>
     </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>545</v>
       </c>
@@ -2633,7 +5027,7 @@
         <v>9.5143000000000005E-2</v>
       </c>
     </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>550</v>
       </c>
@@ -2641,7 +5035,7 @@
         <v>9.7606999999999999E-2</v>
       </c>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>555</v>
       </c>
@@ -2649,7 +5043,7 @@
         <v>0.100643</v>
       </c>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>560</v>
       </c>
@@ -2657,7 +5051,7 @@
         <v>0.103786</v>
       </c>
     </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>565</v>
       </c>
@@ -2665,7 +5059,7 @@
         <v>0.10610700000000001</v>
       </c>
     </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>570</v>
       </c>
@@ -2673,7 +5067,7 @@
         <v>0.10878599999999999</v>
       </c>
     </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>575</v>
       </c>
@@ -2681,7 +5075,7 @@
         <v>0.11264299999999999</v>
       </c>
     </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>580</v>
       </c>
@@ -2689,7 +5083,7 @@
         <v>0.115857</v>
       </c>
     </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>585</v>
       </c>
@@ -2697,7 +5091,7 @@
         <v>0.117643</v>
       </c>
     </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>590</v>
       </c>
@@ -2705,7 +5099,7 @@
         <v>0.12042899999999999</v>
       </c>
     </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>595</v>
       </c>
@@ -2713,7 +5107,7 @@
         <v>0.12385699999999999</v>
       </c>
     </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>600</v>
       </c>
@@ -2721,7 +5115,7 @@
         <v>0.12671399999999999</v>
       </c>
     </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>605</v>
       </c>
@@ -2729,7 +5123,7 @@
         <v>0.130107</v>
       </c>
     </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>610</v>
       </c>
@@ -2737,7 +5131,7 @@
         <v>0.13292899999999999</v>
       </c>
     </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>615</v>
       </c>
@@ -2745,7 +5139,7 @@
         <v>0.136714</v>
       </c>
     </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>620</v>
       </c>
@@ -2753,7 +5147,7 @@
         <v>0.139821</v>
       </c>
     </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>625</v>
       </c>
@@ -2761,7 +5155,7 @@
         <v>0.14496400000000001</v>
       </c>
     </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>630</v>
       </c>
@@ -2769,7 +5163,7 @@
         <v>0.14660699999999999</v>
       </c>
     </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>635</v>
       </c>
@@ -2777,7 +5171,7 @@
         <v>0.15346399999999999</v>
       </c>
     </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>640</v>
       </c>
@@ -2785,7 +5179,7 @@
         <v>0.15378600000000001</v>
       </c>
     </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>645</v>
       </c>
@@ -2793,7 +5187,7 @@
         <v>0.157357</v>
       </c>
     </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>650</v>
       </c>
@@ -2801,7 +5195,7 @@
         <v>0.160714</v>
       </c>
     </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>655</v>
       </c>
@@ -2809,7 +5203,7 @@
         <v>0.16492899999999999</v>
       </c>
     </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>660</v>
       </c>
@@ -2817,7 +5211,7 @@
         <v>0.167821</v>
       </c>
     </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>665</v>
       </c>
@@ -2825,7 +5219,7 @@
         <v>0.172571</v>
       </c>
     </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>670</v>
       </c>
@@ -2833,7 +5227,7 @@
         <v>0.17582100000000001</v>
       </c>
     </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>675</v>
       </c>
@@ -2841,7 +5235,7 @@
         <v>0.18010699999999999</v>
       </c>
     </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>680</v>
       </c>
@@ -2849,7 +5243,7 @@
         <v>0.18671399999999999</v>
       </c>
     </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>685</v>
       </c>
@@ -2857,7 +5251,7 @@
         <v>0.18792900000000001</v>
       </c>
     </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>690</v>
       </c>
@@ -2865,7 +5259,7 @@
         <v>0.19214300000000001</v>
       </c>
     </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>695</v>
       </c>
@@ -2873,7 +5267,7 @@
         <v>0.19717899999999999</v>
       </c>
     </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B142">
         <v>700</v>
       </c>
@@ -2881,7 +5275,7 @@
         <v>0.200321</v>
       </c>
     </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>705</v>
       </c>
@@ -2889,7 +5283,7 @@
         <v>0.20474999999999999</v>
       </c>
     </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>710</v>
       </c>
@@ -2897,7 +5291,7 @@
         <v>0.20921400000000001</v>
       </c>
     </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>715</v>
       </c>
@@ -2905,7 +5299,7 @@
         <v>0.213536</v>
       </c>
     </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>720</v>
       </c>
@@ -2913,7 +5307,7 @@
         <v>0.22067899999999999</v>
       </c>
     </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>725</v>
       </c>
@@ -2921,7 +5315,7 @@
         <v>0.22257099999999999</v>
       </c>
     </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>730</v>
       </c>
@@ -2929,7 +5323,7 @@
         <v>0.22657099999999999</v>
       </c>
     </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>735</v>
       </c>
@@ -2937,7 +5331,7 @@
         <v>0.23153599999999999</v>
       </c>
     </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>740</v>
       </c>
@@ -2945,7 +5339,7 @@
         <v>0.23646400000000001</v>
       </c>
     </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>745</v>
       </c>
@@ -2953,7 +5347,7 @@
         <v>0.24046400000000001</v>
       </c>
     </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>750</v>
       </c>
@@ -2961,7 +5355,7 @@
         <v>0.24621399999999999</v>
       </c>
     </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>755</v>
       </c>
@@ -2969,7 +5363,7 @@
         <v>0.25432100000000002</v>
       </c>
     </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>760</v>
       </c>
@@ -2977,7 +5371,7 @@
         <v>0.25567899999999999</v>
       </c>
     </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B155">
         <v>765</v>
       </c>
@@ -2985,7 +5379,7 @@
         <v>0.26035700000000001</v>
       </c>
     </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>770</v>
       </c>
@@ -2993,7 +5387,7 @@
         <v>0.26589299999999999</v>
       </c>
     </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>775</v>
       </c>
@@ -3001,7 +5395,7 @@
         <v>0.27232099999999998</v>
       </c>
     </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B158">
         <v>780</v>
       </c>
@@ -3009,7 +5403,7 @@
         <v>0.27746399999999999</v>
       </c>
     </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B159">
         <v>785</v>
       </c>
@@ -3017,7 +5411,7 @@
         <v>0.28499999999999998</v>
       </c>
     </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B160">
         <v>790</v>
       </c>
@@ -3025,7 +5419,7 @@
         <v>0.28849999999999998</v>
       </c>
     </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>795</v>
       </c>
@@ -3033,7 +5427,7 @@
         <v>0.29328599999999999</v>
       </c>
     </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B162">
         <v>800</v>
       </c>
@@ -3041,7 +5435,7 @@
         <v>0.29807099999999997</v>
       </c>
     </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B163">
         <v>805</v>
       </c>
@@ -3049,7 +5443,7 @@
         <v>0.30396400000000001</v>
       </c>
     </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B164">
         <v>810</v>
       </c>
@@ -3057,7 +5451,7 @@
         <v>0.30917899999999998</v>
       </c>
     </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>815</v>
       </c>
@@ -3065,7 +5459,7 @@
         <v>0.31896400000000003</v>
       </c>
     </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B166">
         <v>820</v>
       </c>
@@ -3073,7 +5467,7 @@
         <v>0.32060699999999998</v>
       </c>
     </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B167">
         <v>825</v>
       </c>
@@ -3081,7 +5475,7 @@
         <v>0.32628600000000002</v>
       </c>
     </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B168">
         <v>830</v>
       </c>
@@ -3089,7 +5483,7 @@
         <v>0.332536</v>
       </c>
     </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B169">
         <v>835</v>
       </c>
@@ -3097,7 +5491,7 @@
         <v>0.33774999999999999</v>
       </c>
     </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B170">
         <v>840</v>
       </c>
@@ -3105,7 +5499,7 @@
         <v>0.34735700000000003</v>
       </c>
     </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>845</v>
       </c>
@@ -3113,7 +5507,7 @@
         <v>0.35057100000000002</v>
       </c>
     </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B172">
         <v>850</v>
       </c>
@@ -3121,7 +5515,7 @@
         <v>0.35760700000000001</v>
       </c>
     </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B173">
         <v>855</v>
       </c>
@@ -3129,7 +5523,7 @@
         <v>0.36303600000000003</v>
       </c>
     </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B174">
         <v>860</v>
       </c>
@@ -3137,7 +5531,7 @@
         <v>0.36932100000000001</v>
       </c>
     </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>865</v>
       </c>
@@ -3145,7 +5539,7 @@
         <v>0.38128600000000001</v>
       </c>
     </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B176">
         <v>870</v>
       </c>
@@ -3153,7 +5547,7 @@
         <v>0.382714</v>
       </c>
     </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B177">
         <v>875</v>
       </c>
@@ -3161,7 +5555,7 @@
         <v>0.38964300000000002</v>
       </c>
     </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>880</v>
       </c>
@@ -3169,7 +5563,7 @@
         <v>0.396393</v>
       </c>
     </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B179">
         <v>885</v>
       </c>
@@ -3177,7 +5571,7 @@
         <v>0.40475</v>
       </c>
     </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B180">
         <v>890</v>
       </c>
@@ -3185,7 +5579,7 @@
         <v>0.41092899999999999</v>
       </c>
     </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B181">
         <v>895</v>
       </c>
@@ -3193,7 +5587,7 @@
         <v>0.416821</v>
       </c>
     </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B182">
         <v>900</v>
       </c>
@@ -3201,7 +5595,7 @@
         <v>0.42285699999999998</v>
       </c>
     </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B183">
         <v>905</v>
       </c>
@@ -3209,7 +5603,7 @@
         <v>0.43071399999999999</v>
       </c>
     </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B184">
         <v>910</v>
       </c>
@@ -3217,7 +5611,7 @@
         <v>0.44132100000000002</v>
       </c>
     </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B185">
         <v>915</v>
       </c>
@@ -3225,7 +5619,7 @@
         <v>0.44428600000000001</v>
       </c>
     </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B186">
         <v>920</v>
       </c>
@@ -3233,7 +5627,7 @@
         <v>0.453679</v>
       </c>
     </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B187">
         <v>925</v>
       </c>
@@ -3241,7 +5635,7 @@
         <v>0.45824999999999999</v>
       </c>
     </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B188">
         <v>930</v>
       </c>
@@ -3249,7 +5643,7 @@
         <v>0.46850000000000003</v>
       </c>
     </row>
-    <row r="189" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B189">
         <v>935</v>
       </c>
@@ -3257,7 +5651,7 @@
         <v>0.474464</v>
       </c>
     </row>
-    <row r="190" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B190">
         <v>940</v>
       </c>
@@ -3265,7 +5659,7 @@
         <v>0.48125000000000001</v>
       </c>
     </row>
-    <row r="191" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B191">
         <v>945</v>
       </c>
@@ -3273,7 +5667,7 @@
         <v>0.49267899999999998</v>
       </c>
     </row>
-    <row r="192" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B192">
         <v>950</v>
       </c>
@@ -3281,7 +5675,7 @@
         <v>0.49807099999999999</v>
       </c>
     </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B193">
         <v>955</v>
       </c>
@@ -3289,7 +5683,7 @@
         <v>0.50592899999999996</v>
       </c>
     </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B194">
         <v>960</v>
       </c>
@@ -3297,7 +5691,7 @@
         <v>0.51324999999999998</v>
       </c>
     </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B195">
         <v>965</v>
       </c>
@@ -3305,7 +5699,7 @@
         <v>0.52514300000000003</v>
       </c>
     </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B196">
         <v>970</v>
       </c>
@@ -3313,7 +5707,7 @@
         <v>0.52964299999999997</v>
       </c>
     </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B197">
         <v>975</v>
       </c>
@@ -3321,7 +5715,7 @@
         <v>0.53725000000000001</v>
       </c>
     </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B198">
         <v>980</v>
       </c>
@@ -3329,7 +5723,7 @@
         <v>0.54900000000000004</v>
       </c>
     </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B199">
         <v>985</v>
       </c>
@@ -3337,7 +5731,7 @@
         <v>0.553643</v>
       </c>
     </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B200">
         <v>990</v>
       </c>
@@ -3345,7 +5739,7 @@
         <v>0.56271400000000005</v>
       </c>
     </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B201">
         <v>995</v>
       </c>
@@ -3353,7 +5747,7 @@
         <v>0.57492900000000002</v>
       </c>
     </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B202">
         <v>1000</v>
       </c>

--- a/G_arbol_expansion_minima/graficas.xlsx
+++ b/G_arbol_expansion_minima/graficas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\posgrado\analisis_algoritmos\G_arbol_expansion_minima\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBF57A62-DA35-407D-92A1-F69D448618AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B55A2F-A3C1-4B22-99E4-415DBC2CE92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,9 +28,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t>kruscal</t>
+  </si>
+  <si>
+    <t>nuevo</t>
   </si>
 </sst>
 </file>
@@ -131,17 +134,7 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.10553701461093383"/>
-          <c:y val="9.2788689246200692E-2"/>
-          <c:w val="0.71601772971261202"/>
-          <c:h val="0.72807545585104017"/>
-        </c:manualLayout>
-      </c:layout>
+      <c:layout/>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -149,7 +142,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Prim</c:v>
+            <c:v>Kruskal(ms)</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -177,619 +170,169 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Hoja1!$B$3:$B$202</c:f>
+              <c:f>Hoja1!$J$29:$J$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="200"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
-                  <c:v>5</c:v>
+                  <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>15</c:v>
+                  <c:v>50</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>20</c:v>
+                  <c:v>70</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>25</c:v>
+                  <c:v>90</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30</c:v>
+                  <c:v>110</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>35</c:v>
+                  <c:v>130</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>40</c:v>
+                  <c:v>150</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>45</c:v>
+                  <c:v>170</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>50</c:v>
+                  <c:v>190</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>55</c:v>
+                  <c:v>210</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>60</c:v>
+                  <c:v>230</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>65</c:v>
+                  <c:v>250</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>70</c:v>
+                  <c:v>270</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>75</c:v>
+                  <c:v>290</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>80</c:v>
+                  <c:v>310</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>85</c:v>
+                  <c:v>330</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>90</c:v>
+                  <c:v>350</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>95</c:v>
+                  <c:v>370</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>100</c:v>
+                  <c:v>390</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>105</c:v>
+                  <c:v>410</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>110</c:v>
+                  <c:v>430</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>115</c:v>
+                  <c:v>450</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>120</c:v>
+                  <c:v>470</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>125</c:v>
+                  <c:v>490</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>130</c:v>
+                  <c:v>510</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>135</c:v>
+                  <c:v>530</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>140</c:v>
+                  <c:v>550</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>145</c:v>
+                  <c:v>570</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>150</c:v>
+                  <c:v>590</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>155</c:v>
+                  <c:v>610</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>160</c:v>
+                  <c:v>630</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>165</c:v>
+                  <c:v>650</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>170</c:v>
+                  <c:v>670</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>175</c:v>
+                  <c:v>690</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>180</c:v>
+                  <c:v>710</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>185</c:v>
+                  <c:v>730</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>190</c:v>
+                  <c:v>750</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>195</c:v>
+                  <c:v>770</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>200</c:v>
+                  <c:v>790</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>205</c:v>
+                  <c:v>810</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>210</c:v>
+                  <c:v>830</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>215</c:v>
+                  <c:v>850</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>220</c:v>
+                  <c:v>870</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>225</c:v>
+                  <c:v>890</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>230</c:v>
+                  <c:v>910</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>235</c:v>
+                  <c:v>930</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>240</c:v>
+                  <c:v>950</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>245</c:v>
+                  <c:v>970</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>250</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>255</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>260</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>265</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>270</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>275</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>280</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>285</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>290</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>295</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>300</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>305</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>310</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>315</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>320</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>325</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>330</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>335</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>340</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>345</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>350</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>355</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>360</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>365</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>370</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>375</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>380</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>385</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>390</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>395</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>400</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>405</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>410</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>415</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>420</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>425</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>430</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>435</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>440</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>445</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>450</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>455</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>460</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>465</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>470</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>475</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>480</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>485</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>490</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>495</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>500</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>505</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>510</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>515</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>520</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>525</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>530</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>535</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>540</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>545</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>550</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>555</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>560</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>565</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>570</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>575</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>580</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>585</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>590</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>595</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>600</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>605</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>610</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>615</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>620</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>625</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>630</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>635</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>640</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>645</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>650</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>655</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>660</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>665</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>670</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>675</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>680</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>685</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>690</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>695</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>700</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>705</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>710</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>715</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>720</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>725</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>730</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>735</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>740</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>745</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>750</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>755</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>760</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>765</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>770</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>775</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>780</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>785</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>790</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>795</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>800</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>805</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>810</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>815</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>820</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>825</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>830</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>835</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>840</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>845</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>850</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>855</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>860</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>865</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>870</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>875</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>880</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>885</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>890</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>895</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>900</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>905</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>910</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>915</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>920</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>925</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>930</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>935</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>940</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>945</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>950</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>955</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>960</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>965</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>970</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>975</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>980</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>985</c:v>
-                </c:pt>
-                <c:pt idx="197">
                   <c:v>990</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>995</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Hoja1!$C$3:$C$202</c:f>
+              <c:f>Hoja1!$K$29:$K$78</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="200"/>
+                <c:ptCount val="50"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -809,586 +352,136 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>3.6000000000000001E-5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>7.1000000000000005E-5</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.1000000000000005E-5</c:v>
+                  <c:v>0.107143</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.4300000000000001E-4</c:v>
+                  <c:v>7.1429000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.07E-4</c:v>
+                  <c:v>7.1429000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.7899999999999999E-4</c:v>
+                  <c:v>0.214286</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.5000000000000001E-4</c:v>
+                  <c:v>7.1429000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.7899999999999999E-4</c:v>
+                  <c:v>7.1429000000000006E-2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>1.7899999999999999E-4</c:v>
+                  <c:v>0.107143</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>4.2900000000000002E-4</c:v>
+                  <c:v>0.17857100000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>3.21E-4</c:v>
+                  <c:v>0.32142900000000002</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>5.0000000000000001E-4</c:v>
+                  <c:v>0.28571400000000002</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>3.9300000000000001E-4</c:v>
+                  <c:v>0.35714299999999999</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>6.7900000000000002E-4</c:v>
+                  <c:v>0.32142900000000002</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>7.8600000000000002E-4</c:v>
+                  <c:v>0.57142899999999996</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>8.9300000000000002E-4</c:v>
+                  <c:v>0.46428599999999998</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>1E-3</c:v>
+                  <c:v>0.53571400000000002</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>1.0709999999999999E-3</c:v>
+                  <c:v>0.39285700000000001</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>1.25E-3</c:v>
+                  <c:v>0.57142899999999996</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>1.3209999999999999E-3</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>1.5709999999999999E-3</c:v>
+                  <c:v>0.42857099999999998</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>1.786E-3</c:v>
+                  <c:v>0.57142899999999996</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>2E-3</c:v>
+                  <c:v>0.71428599999999998</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>2.2859999999999998E-3</c:v>
+                  <c:v>0.82142899999999996</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>2.4290000000000002E-3</c:v>
+                  <c:v>0.96428599999999998</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>2.6069999999999999E-3</c:v>
+                  <c:v>0.89285700000000001</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>2.8570000000000002E-3</c:v>
+                  <c:v>0.96428599999999998</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>3.0360000000000001E-3</c:v>
+                  <c:v>0.96428599999999998</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>3.107E-3</c:v>
+                  <c:v>1.035714</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>3.7859999999999999E-3</c:v>
+                  <c:v>1.071429</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>4.0000000000000001E-3</c:v>
+                  <c:v>1.071429</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>4.3930000000000002E-3</c:v>
+                  <c:v>1.214286</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>4.4640000000000001E-3</c:v>
+                  <c:v>1.25</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>5.0000000000000001E-3</c:v>
+                  <c:v>1.321429</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>5.4289999999999998E-3</c:v>
+                  <c:v>1.357143</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>5.7860000000000003E-3</c:v>
+                  <c:v>1.428571</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>6.2139999999999999E-3</c:v>
+                  <c:v>1.464286</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>6.8929999999999998E-3</c:v>
+                  <c:v>1.785714</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>7.0359999999999997E-3</c:v>
+                  <c:v>1.714286</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>7.4640000000000001E-3</c:v>
+                  <c:v>1.892857</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>8.0000000000000002E-3</c:v>
+                  <c:v>1.857143</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>8.6070000000000001E-3</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>8.9999999999999993E-3</c:v>
+                  <c:v>2.0714290000000002</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>9.6430000000000005E-3</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>1.0142999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="51">
-                  <c:v>1.0678999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="52">
-                  <c:v>1.1285999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="53">
-                  <c:v>1.1964000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="54">
-                  <c:v>1.2678999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="55">
-                  <c:v>1.3285999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="56">
-                  <c:v>1.4071E-2</c:v>
-                </c:pt>
-                <c:pt idx="57">
-                  <c:v>1.4321E-2</c:v>
-                </c:pt>
-                <c:pt idx="58">
-                  <c:v>1.5535999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="59">
-                  <c:v>1.6463999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="60">
-                  <c:v>1.7107000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="61">
-                  <c:v>1.8107000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="62">
-                  <c:v>1.8643E-2</c:v>
-                </c:pt>
-                <c:pt idx="63">
-                  <c:v>1.9963999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="64">
-                  <c:v>2.0607E-2</c:v>
-                </c:pt>
-                <c:pt idx="65">
-                  <c:v>2.1714000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="66">
-                  <c:v>2.2536E-2</c:v>
-                </c:pt>
-                <c:pt idx="67">
-                  <c:v>2.3643000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="68">
-                  <c:v>2.4535999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="69">
-                  <c:v>2.5786E-2</c:v>
-                </c:pt>
-                <c:pt idx="70">
-                  <c:v>2.6856999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="71">
-                  <c:v>2.8035999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="72">
-                  <c:v>2.9749999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="73">
-                  <c:v>3.0321000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="74">
-                  <c:v>3.1928999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="75">
-                  <c:v>3.3429E-2</c:v>
-                </c:pt>
-                <c:pt idx="76">
-                  <c:v>3.4679000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="77">
-                  <c:v>3.5785999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="78">
-                  <c:v>3.6679000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="79">
-                  <c:v>3.8071000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="80">
-                  <c:v>3.9607000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="81">
-                  <c:v>4.0856999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="82">
-                  <c:v>4.2606999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="83">
-                  <c:v>4.4249999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="84">
-                  <c:v>4.5678999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="85">
-                  <c:v>4.7071000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="86">
-                  <c:v>4.9070999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="87">
-                  <c:v>5.0285999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="88">
-                  <c:v>5.2357000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="89">
-                  <c:v>5.3928999999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="90">
-                  <c:v>5.6000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="91">
-                  <c:v>5.7964000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="92">
-                  <c:v>5.9464000000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="93">
-                  <c:v>6.1607000000000002E-2</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>6.3535999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>6.5679000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>6.7785999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>6.9642999999999997E-2</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>7.1714E-2</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>7.5036000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>7.8E-2</c:v>
-                </c:pt>
-                <c:pt idx="101">
-                  <c:v>7.9000000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="102">
-                  <c:v>8.0679000000000001E-2</c:v>
-                </c:pt>
-                <c:pt idx="103">
-                  <c:v>8.2392999999999994E-2</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>8.5142999999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>8.7320999999999996E-2</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>9.0428999999999995E-2</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>9.2964000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>9.5143000000000005E-2</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>9.7606999999999999E-2</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>0.100643</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>0.103786</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>0.10610700000000001</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>0.10878599999999999</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>0.11264299999999999</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>0.115857</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>0.117643</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>0.12042899999999999</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>0.12385699999999999</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>0.12671399999999999</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>0.130107</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>0.13292899999999999</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>0.136714</c:v>
-                </c:pt>
-                <c:pt idx="123">
-                  <c:v>0.139821</c:v>
-                </c:pt>
-                <c:pt idx="124">
-                  <c:v>0.14496400000000001</c:v>
-                </c:pt>
-                <c:pt idx="125">
-                  <c:v>0.14660699999999999</c:v>
-                </c:pt>
-                <c:pt idx="126">
-                  <c:v>0.15346399999999999</c:v>
-                </c:pt>
-                <c:pt idx="127">
-                  <c:v>0.15378600000000001</c:v>
-                </c:pt>
-                <c:pt idx="128">
-                  <c:v>0.157357</c:v>
-                </c:pt>
-                <c:pt idx="129">
-                  <c:v>0.160714</c:v>
-                </c:pt>
-                <c:pt idx="130">
-                  <c:v>0.16492899999999999</c:v>
-                </c:pt>
-                <c:pt idx="131">
-                  <c:v>0.167821</c:v>
-                </c:pt>
-                <c:pt idx="132">
-                  <c:v>0.172571</c:v>
-                </c:pt>
-                <c:pt idx="133">
-                  <c:v>0.17582100000000001</c:v>
-                </c:pt>
-                <c:pt idx="134">
-                  <c:v>0.18010699999999999</c:v>
-                </c:pt>
-                <c:pt idx="135">
-                  <c:v>0.18671399999999999</c:v>
-                </c:pt>
-                <c:pt idx="136">
-                  <c:v>0.18792900000000001</c:v>
-                </c:pt>
-                <c:pt idx="137">
-                  <c:v>0.19214300000000001</c:v>
-                </c:pt>
-                <c:pt idx="138">
-                  <c:v>0.19717899999999999</c:v>
-                </c:pt>
-                <c:pt idx="139">
-                  <c:v>0.200321</c:v>
-                </c:pt>
-                <c:pt idx="140">
-                  <c:v>0.20474999999999999</c:v>
-                </c:pt>
-                <c:pt idx="141">
-                  <c:v>0.20921400000000001</c:v>
-                </c:pt>
-                <c:pt idx="142">
-                  <c:v>0.213536</c:v>
-                </c:pt>
-                <c:pt idx="143">
-                  <c:v>0.22067899999999999</c:v>
-                </c:pt>
-                <c:pt idx="144">
-                  <c:v>0.22257099999999999</c:v>
-                </c:pt>
-                <c:pt idx="145">
-                  <c:v>0.22657099999999999</c:v>
-                </c:pt>
-                <c:pt idx="146">
-                  <c:v>0.23153599999999999</c:v>
-                </c:pt>
-                <c:pt idx="147">
-                  <c:v>0.23646400000000001</c:v>
-                </c:pt>
-                <c:pt idx="148">
-                  <c:v>0.24046400000000001</c:v>
-                </c:pt>
-                <c:pt idx="149">
-                  <c:v>0.24621399999999999</c:v>
-                </c:pt>
-                <c:pt idx="150">
-                  <c:v>0.25432100000000002</c:v>
-                </c:pt>
-                <c:pt idx="151">
-                  <c:v>0.25567899999999999</c:v>
-                </c:pt>
-                <c:pt idx="152">
-                  <c:v>0.26035700000000001</c:v>
-                </c:pt>
-                <c:pt idx="153">
-                  <c:v>0.26589299999999999</c:v>
-                </c:pt>
-                <c:pt idx="154">
-                  <c:v>0.27232099999999998</c:v>
-                </c:pt>
-                <c:pt idx="155">
-                  <c:v>0.27746399999999999</c:v>
-                </c:pt>
-                <c:pt idx="156">
-                  <c:v>0.28499999999999998</c:v>
-                </c:pt>
-                <c:pt idx="157">
-                  <c:v>0.28849999999999998</c:v>
-                </c:pt>
-                <c:pt idx="158">
-                  <c:v>0.29328599999999999</c:v>
-                </c:pt>
-                <c:pt idx="159">
-                  <c:v>0.29807099999999997</c:v>
-                </c:pt>
-                <c:pt idx="160">
-                  <c:v>0.30396400000000001</c:v>
-                </c:pt>
-                <c:pt idx="161">
-                  <c:v>0.30917899999999998</c:v>
-                </c:pt>
-                <c:pt idx="162">
-                  <c:v>0.31896400000000003</c:v>
-                </c:pt>
-                <c:pt idx="163">
-                  <c:v>0.32060699999999998</c:v>
-                </c:pt>
-                <c:pt idx="164">
-                  <c:v>0.32628600000000002</c:v>
-                </c:pt>
-                <c:pt idx="165">
-                  <c:v>0.332536</c:v>
-                </c:pt>
-                <c:pt idx="166">
-                  <c:v>0.33774999999999999</c:v>
-                </c:pt>
-                <c:pt idx="167">
-                  <c:v>0.34735700000000003</c:v>
-                </c:pt>
-                <c:pt idx="168">
-                  <c:v>0.35057100000000002</c:v>
-                </c:pt>
-                <c:pt idx="169">
-                  <c:v>0.35760700000000001</c:v>
-                </c:pt>
-                <c:pt idx="170">
-                  <c:v>0.36303600000000003</c:v>
-                </c:pt>
-                <c:pt idx="171">
-                  <c:v>0.36932100000000001</c:v>
-                </c:pt>
-                <c:pt idx="172">
-                  <c:v>0.38128600000000001</c:v>
-                </c:pt>
-                <c:pt idx="173">
-                  <c:v>0.382714</c:v>
-                </c:pt>
-                <c:pt idx="174">
-                  <c:v>0.38964300000000002</c:v>
-                </c:pt>
-                <c:pt idx="175">
-                  <c:v>0.396393</c:v>
-                </c:pt>
-                <c:pt idx="176">
-                  <c:v>0.40475</c:v>
-                </c:pt>
-                <c:pt idx="177">
-                  <c:v>0.41092899999999999</c:v>
-                </c:pt>
-                <c:pt idx="178">
-                  <c:v>0.416821</c:v>
-                </c:pt>
-                <c:pt idx="179">
-                  <c:v>0.42285699999999998</c:v>
-                </c:pt>
-                <c:pt idx="180">
-                  <c:v>0.43071399999999999</c:v>
-                </c:pt>
-                <c:pt idx="181">
-                  <c:v>0.44132100000000002</c:v>
-                </c:pt>
-                <c:pt idx="182">
-                  <c:v>0.44428600000000001</c:v>
-                </c:pt>
-                <c:pt idx="183">
-                  <c:v>0.453679</c:v>
-                </c:pt>
-                <c:pt idx="184">
-                  <c:v>0.45824999999999999</c:v>
-                </c:pt>
-                <c:pt idx="185">
-                  <c:v>0.46850000000000003</c:v>
-                </c:pt>
-                <c:pt idx="186">
-                  <c:v>0.474464</c:v>
-                </c:pt>
-                <c:pt idx="187">
-                  <c:v>0.48125000000000001</c:v>
-                </c:pt>
-                <c:pt idx="188">
-                  <c:v>0.49267899999999998</c:v>
-                </c:pt>
-                <c:pt idx="189">
-                  <c:v>0.49807099999999999</c:v>
-                </c:pt>
-                <c:pt idx="190">
-                  <c:v>0.50592899999999996</c:v>
-                </c:pt>
-                <c:pt idx="191">
-                  <c:v>0.51324999999999998</c:v>
-                </c:pt>
-                <c:pt idx="192">
-                  <c:v>0.52514300000000003</c:v>
-                </c:pt>
-                <c:pt idx="193">
-                  <c:v>0.52964299999999997</c:v>
-                </c:pt>
-                <c:pt idx="194">
-                  <c:v>0.53725000000000001</c:v>
-                </c:pt>
-                <c:pt idx="195">
-                  <c:v>0.54900000000000004</c:v>
-                </c:pt>
-                <c:pt idx="196">
-                  <c:v>0.553643</c:v>
-                </c:pt>
-                <c:pt idx="197">
-                  <c:v>0.56271400000000005</c:v>
-                </c:pt>
-                <c:pt idx="198">
-                  <c:v>0.57492900000000002</c:v>
-                </c:pt>
-                <c:pt idx="199">
-                  <c:v>0.57892900000000003</c:v>
+                  <c:v>2.1071430000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1396,7 +489,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-E235-407C-90F5-259EFDF30DEE}"/>
+              <c16:uniqueId val="{00000000-FC1B-43F9-902D-DF59506D16F9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1723,6 +816,31 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX"/>
+              <a:t>Prim</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1754,7 +872,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.10553701461093383"/>
+          <c:y val="9.2788689246200692E-2"/>
+          <c:w val="0.71601772971261202"/>
+          <c:h val="0.72807545585104017"/>
+        </c:manualLayout>
+      </c:layout>
       <c:scatterChart>
         <c:scatterStyle val="lineMarker"/>
         <c:varyColors val="0"/>
@@ -1762,7 +890,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:v>Kruskal(ms)</c:v>
+            <c:v>Prim</c:v>
           </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
@@ -1790,169 +918,610 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>Hoja1!$J$29:$J$78</c:f>
+              <c:f>Hoja1!$E$3:$E$199</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="197"/>
                 <c:pt idx="0">
-                  <c:v>10</c:v>
+                  <c:v>20</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>30</c:v>
                 </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>50</c:v>
                 </c:pt>
-                <c:pt idx="3">
+                <c:pt idx="7">
+                  <c:v>55</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>70</c:v>
                 </c:pt>
-                <c:pt idx="4">
+                <c:pt idx="11">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="14">
                   <c:v>90</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="15">
+                  <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>105</c:v>
+                </c:pt>
+                <c:pt idx="18">
                   <c:v>110</c:v>
                 </c:pt>
-                <c:pt idx="6">
+                <c:pt idx="19">
+                  <c:v>115</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>120</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>125</c:v>
+                </c:pt>
+                <c:pt idx="22">
                   <c:v>130</c:v>
                 </c:pt>
-                <c:pt idx="7">
+                <c:pt idx="23">
+                  <c:v>135</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>140</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>145</c:v>
+                </c:pt>
+                <c:pt idx="26">
                   <c:v>150</c:v>
                 </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="27">
+                  <c:v>155</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>160</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>165</c:v>
+                </c:pt>
+                <c:pt idx="30">
                   <c:v>170</c:v>
                 </c:pt>
-                <c:pt idx="9">
+                <c:pt idx="31">
+                  <c:v>175</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>180</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>185</c:v>
+                </c:pt>
+                <c:pt idx="34">
                   <c:v>190</c:v>
                 </c:pt>
-                <c:pt idx="10">
+                <c:pt idx="35">
+                  <c:v>195</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>205</c:v>
+                </c:pt>
+                <c:pt idx="38">
                   <c:v>210</c:v>
                 </c:pt>
-                <c:pt idx="11">
+                <c:pt idx="39">
+                  <c:v>215</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>220</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>225</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>230</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="43">
+                  <c:v>235</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>240</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="46">
                   <c:v>250</c:v>
                 </c:pt>
-                <c:pt idx="13">
+                <c:pt idx="47">
+                  <c:v>255</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>260</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>265</c:v>
+                </c:pt>
+                <c:pt idx="50">
                   <c:v>270</c:v>
                 </c:pt>
-                <c:pt idx="14">
+                <c:pt idx="51">
+                  <c:v>275</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>280</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>285</c:v>
+                </c:pt>
+                <c:pt idx="54">
                   <c:v>290</c:v>
                 </c:pt>
-                <c:pt idx="15">
+                <c:pt idx="55">
+                  <c:v>295</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>300</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>305</c:v>
+                </c:pt>
+                <c:pt idx="58">
                   <c:v>310</c:v>
                 </c:pt>
-                <c:pt idx="16">
+                <c:pt idx="59">
+                  <c:v>315</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>320</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>325</c:v>
+                </c:pt>
+                <c:pt idx="62">
                   <c:v>330</c:v>
                 </c:pt>
-                <c:pt idx="17">
+                <c:pt idx="63">
+                  <c:v>335</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>340</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>345</c:v>
+                </c:pt>
+                <c:pt idx="66">
                   <c:v>350</c:v>
                 </c:pt>
-                <c:pt idx="18">
+                <c:pt idx="67">
+                  <c:v>355</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>360</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>365</c:v>
+                </c:pt>
+                <c:pt idx="70">
                   <c:v>370</c:v>
                 </c:pt>
-                <c:pt idx="19">
+                <c:pt idx="71">
+                  <c:v>375</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>380</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>385</c:v>
+                </c:pt>
+                <c:pt idx="74">
                   <c:v>390</c:v>
                 </c:pt>
-                <c:pt idx="20">
+                <c:pt idx="75">
+                  <c:v>395</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>405</c:v>
+                </c:pt>
+                <c:pt idx="78">
                   <c:v>410</c:v>
                 </c:pt>
-                <c:pt idx="21">
+                <c:pt idx="79">
+                  <c:v>415</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>425</c:v>
+                </c:pt>
+                <c:pt idx="82">
                   <c:v>430</c:v>
                 </c:pt>
-                <c:pt idx="22">
+                <c:pt idx="83">
+                  <c:v>435</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>440</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="86">
                   <c:v>450</c:v>
                 </c:pt>
-                <c:pt idx="23">
+                <c:pt idx="87">
+                  <c:v>455</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>460</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>465</c:v>
+                </c:pt>
+                <c:pt idx="90">
                   <c:v>470</c:v>
                 </c:pt>
-                <c:pt idx="24">
+                <c:pt idx="91">
+                  <c:v>475</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>480</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>485</c:v>
+                </c:pt>
+                <c:pt idx="94">
                   <c:v>490</c:v>
                 </c:pt>
-                <c:pt idx="25">
+                <c:pt idx="95">
+                  <c:v>495</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>505</c:v>
+                </c:pt>
+                <c:pt idx="98">
                   <c:v>510</c:v>
                 </c:pt>
-                <c:pt idx="26">
+                <c:pt idx="99">
+                  <c:v>515</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>520</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>525</c:v>
+                </c:pt>
+                <c:pt idx="102">
                   <c:v>530</c:v>
                 </c:pt>
-                <c:pt idx="27">
+                <c:pt idx="103">
+                  <c:v>535</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>540</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>545</c:v>
+                </c:pt>
+                <c:pt idx="106">
                   <c:v>550</c:v>
                 </c:pt>
-                <c:pt idx="28">
+                <c:pt idx="107">
+                  <c:v>555</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>560</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>565</c:v>
+                </c:pt>
+                <c:pt idx="110">
                   <c:v>570</c:v>
                 </c:pt>
-                <c:pt idx="29">
+                <c:pt idx="111">
+                  <c:v>575</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>580</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>585</c:v>
+                </c:pt>
+                <c:pt idx="114">
                   <c:v>590</c:v>
                 </c:pt>
-                <c:pt idx="30">
+                <c:pt idx="115">
+                  <c:v>595</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>605</c:v>
+                </c:pt>
+                <c:pt idx="118">
                   <c:v>610</c:v>
                 </c:pt>
-                <c:pt idx="31">
+                <c:pt idx="119">
+                  <c:v>615</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>620</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="122">
                   <c:v>630</c:v>
                 </c:pt>
-                <c:pt idx="32">
+                <c:pt idx="123">
+                  <c:v>635</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>640</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>645</c:v>
+                </c:pt>
+                <c:pt idx="126">
                   <c:v>650</c:v>
                 </c:pt>
-                <c:pt idx="33">
+                <c:pt idx="127">
+                  <c:v>655</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>660</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>665</c:v>
+                </c:pt>
+                <c:pt idx="130">
                   <c:v>670</c:v>
                 </c:pt>
-                <c:pt idx="34">
+                <c:pt idx="131">
+                  <c:v>675</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>680</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>685</c:v>
+                </c:pt>
+                <c:pt idx="134">
                   <c:v>690</c:v>
                 </c:pt>
-                <c:pt idx="35">
+                <c:pt idx="135">
+                  <c:v>695</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>700</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>705</c:v>
+                </c:pt>
+                <c:pt idx="138">
                   <c:v>710</c:v>
                 </c:pt>
-                <c:pt idx="36">
+                <c:pt idx="139">
+                  <c:v>715</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>725</c:v>
+                </c:pt>
+                <c:pt idx="142">
                   <c:v>730</c:v>
                 </c:pt>
-                <c:pt idx="37">
+                <c:pt idx="143">
+                  <c:v>735</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>740</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>745</c:v>
+                </c:pt>
+                <c:pt idx="146">
                   <c:v>750</c:v>
                 </c:pt>
-                <c:pt idx="38">
+                <c:pt idx="147">
+                  <c:v>755</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>760</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>765</c:v>
+                </c:pt>
+                <c:pt idx="150">
                   <c:v>770</c:v>
                 </c:pt>
-                <c:pt idx="39">
+                <c:pt idx="151">
+                  <c:v>775</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>780</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>785</c:v>
+                </c:pt>
+                <c:pt idx="154">
                   <c:v>790</c:v>
                 </c:pt>
-                <c:pt idx="40">
+                <c:pt idx="155">
+                  <c:v>795</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>805</c:v>
+                </c:pt>
+                <c:pt idx="158">
                   <c:v>810</c:v>
                 </c:pt>
-                <c:pt idx="41">
+                <c:pt idx="159">
+                  <c:v>815</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>820</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>825</c:v>
+                </c:pt>
+                <c:pt idx="162">
                   <c:v>830</c:v>
                 </c:pt>
-                <c:pt idx="42">
+                <c:pt idx="163">
+                  <c:v>835</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>840</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>845</c:v>
+                </c:pt>
+                <c:pt idx="166">
                   <c:v>850</c:v>
                 </c:pt>
-                <c:pt idx="43">
+                <c:pt idx="167">
+                  <c:v>855</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>860</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>865</c:v>
+                </c:pt>
+                <c:pt idx="170">
                   <c:v>870</c:v>
                 </c:pt>
-                <c:pt idx="44">
+                <c:pt idx="171">
+                  <c:v>875</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>880</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>885</c:v>
+                </c:pt>
+                <c:pt idx="174">
                   <c:v>890</c:v>
                 </c:pt>
-                <c:pt idx="45">
+                <c:pt idx="175">
+                  <c:v>895</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>900</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>905</c:v>
+                </c:pt>
+                <c:pt idx="178">
                   <c:v>910</c:v>
                 </c:pt>
-                <c:pt idx="46">
+                <c:pt idx="179">
+                  <c:v>915</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>920</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>925</c:v>
+                </c:pt>
+                <c:pt idx="182">
                   <c:v>930</c:v>
                 </c:pt>
-                <c:pt idx="47">
+                <c:pt idx="183">
+                  <c:v>935</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>940</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>945</c:v>
+                </c:pt>
+                <c:pt idx="186">
                   <c:v>950</c:v>
                 </c:pt>
-                <c:pt idx="48">
+                <c:pt idx="187">
+                  <c:v>955</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>965</c:v>
+                </c:pt>
+                <c:pt idx="190">
                   <c:v>970</c:v>
                 </c:pt>
-                <c:pt idx="49">
+                <c:pt idx="191">
+                  <c:v>975</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>985</c:v>
+                </c:pt>
+                <c:pt idx="194">
                   <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>995</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>Hoja1!$K$29:$K$78</c:f>
+              <c:f>Hoja1!$D$3:$D$199</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="50"/>
+                <c:ptCount val="197"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -1972,136 +1541,577 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>0</c:v>
+                  <c:v>7.1000000000000005E-5</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0.107143</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>7.1429000000000006E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>7.1429000000000006E-2</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.214286</c:v>
+                  <c:v>3.6000000000000001E-5</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7.1429000000000006E-2</c:v>
+                  <c:v>3.6000000000000001E-5</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>7.1429000000000006E-2</c:v>
+                  <c:v>3.6000000000000001E-5</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.107143</c:v>
+                  <c:v>3.6000000000000001E-5</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.17857100000000001</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.32142900000000002</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.28571400000000002</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.35714299999999999</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>0.32142900000000002</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>0.57142899999999996</c:v>
+                  <c:v>1.07E-4</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>0.46428599999999998</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>0.53571400000000002</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>0.39285700000000001</c:v>
+                  <c:v>1.07E-4</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>0.57142899999999996</c:v>
+                  <c:v>7.1000000000000005E-5</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>0.5</c:v>
+                  <c:v>7.1000000000000005E-5</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>0.42857099999999998</c:v>
+                  <c:v>7.1000000000000005E-5</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>0.57142899999999996</c:v>
+                  <c:v>1.4300000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>0.71428599999999998</c:v>
+                  <c:v>1.7899999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>0.82142899999999996</c:v>
+                  <c:v>3.6000000000000001E-5</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>0.96428599999999998</c:v>
+                  <c:v>7.1000000000000005E-5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>0.89285700000000001</c:v>
+                  <c:v>1.7899999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>0.96428599999999998</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>0.96428599999999998</c:v>
+                  <c:v>2.14E-4</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>1.035714</c:v>
+                  <c:v>1.7899999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>1.071429</c:v>
+                  <c:v>2.14E-4</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>1.071429</c:v>
+                  <c:v>1.7899999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="37">
-                  <c:v>1.214286</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>1.25</c:v>
+                  <c:v>1.7899999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>1.321429</c:v>
+                  <c:v>2.5000000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="40">
-                  <c:v>1.357143</c:v>
+                  <c:v>1.7899999999999999E-4</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>1.428571</c:v>
+                  <c:v>2.8600000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>1.464286</c:v>
+                  <c:v>2.8600000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>1.785714</c:v>
+                  <c:v>1.4300000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="44">
-                  <c:v>1.714286</c:v>
+                  <c:v>2.14E-4</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>1.892857</c:v>
+                  <c:v>2.8600000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>1.857143</c:v>
+                  <c:v>3.21E-4</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>2</c:v>
+                  <c:v>2.8600000000000001E-4</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>2.0714290000000002</c:v>
+                  <c:v>3.57E-4</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>2.1071430000000002</c:v>
+                  <c:v>2.14E-4</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>5.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2.8600000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>5.71E-4</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2.5000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>5.71E-4</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4.2900000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2.14E-4</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>5.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>7.5000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>5.0000000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>4.2900000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>5.3600000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>7.8600000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>5.3600000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>6.7900000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>6.7900000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>7.1400000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>7.5000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>5.71E-4</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>8.5700000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>7.5000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>7.1400000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>7.5000000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>9.2900000000000003E-4</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>7.8600000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>8.9300000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>8.2100000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>9.6400000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>8.2100000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>9.2900000000000003E-4</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>8.9300000000000002E-4</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>9.6400000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>9.6400000000000001E-4</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1.1429999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>1.036E-3</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1.1069999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1.1069999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1.1789999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1.1429999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1E-3</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1.0709999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1.3569999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1.214E-3</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1.286E-3</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>1.3209999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>1.464E-3</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>1.464E-3</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1.3209999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>1.464E-3</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1.286E-3</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>1.536E-3</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>1.5E-3</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1.6069999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1.536E-3</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1.464E-3</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1.464E-3</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>1.5709999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1.8209999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>1.6069999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>1.786E-3</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>1.75E-3</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>1.8209999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>1.9289999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>1.8569999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>1.964E-3</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>1.964E-3</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1.8929999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>2.036E-3</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>1.964E-3</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>2.036E-3</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>2.036E-3</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>2E-3</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>2.0709999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>2.1429999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>2.2139999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>2.1429999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>2.1789999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>2.2139999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>2.2859999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>2.3210000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>2.3930000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>2.464E-3</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>2.464E-3</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>2.3570000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>2.5360000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>2.6069999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>2.5360000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>2.6069999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>2.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>2.7139999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>2.643E-3</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>2.679E-3</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>2.9640000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>2.8930000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>2.8570000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>2.9290000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>2.9290000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>2.9290000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>3.0709999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>3.143E-3</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>3.0360000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>3.2859999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>3.2859999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3.143E-3</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>3.2499999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>3.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>3.3930000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>3.571E-3</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3.5000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>3.7499999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>3.679E-3</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3.643E-3</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3.7859999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>3.9290000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>3.8930000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>3.7499999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>3.8930000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>3.9639999999999996E-3</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>4.0359999999999997E-3</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>4.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>4.2500000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>4.1070000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>4.1070000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>4.2139999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>4.3569999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>4.1790000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>4.3930000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>4.5360000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>4.3930000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>4.4289999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>4.5710000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>4.6430000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>4.7499999999999999E-3</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>4.5710000000000004E-3</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>4.7140000000000003E-3</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>4.8929999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>4.8570000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>4.8570000000000002E-3</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4.8929999999999998E-3</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>5.0000000000000001E-3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2109,7 +2119,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-FC1B-43F9-902D-DF59506D16F9}"/>
+              <c16:uniqueId val="{00000000-087C-4B97-949E-46EA20C1C4E9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3511,27 +3521,29 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>272414</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>463163</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>82867</xdr:rowOff>
+      <xdr:rowOff>16897</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>165984</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>54997</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
+        <xdr:cNvPr id="3" name="Gráfico 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7EC16421-C198-40C5-92A7-6AC92EB3634D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{668DB9A0-AA34-4DC9-A24A-A7B47BC7743D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
@@ -3547,23 +3559,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>502920</xdr:colOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>251792</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>129540</xdr:rowOff>
+      <xdr:rowOff>33131</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>451817</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:rowOff>173895</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2">
+        <xdr:cNvPr id="4" name="Gráfico 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{668DB9A0-AA34-4DC9-A24A-A7B47BC7743D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F6946694-9464-4962-8B1A-155CB51DCCCF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3849,226 +3861,234 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:K202"/>
+  <dimension ref="D2:K199"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B3">
-        <v>5</v>
-      </c>
-      <c r="C3">
+    <row r="2" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>10</v>
-      </c>
-      <c r="C4">
+      <c r="E3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>15</v>
-      </c>
-      <c r="C5">
+      <c r="E4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>20</v>
-      </c>
-      <c r="C6">
+      <c r="E5">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>25</v>
-      </c>
-      <c r="C7">
+      <c r="E6">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B8">
-        <v>30</v>
-      </c>
-      <c r="C8">
+      <c r="E7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>35</v>
-      </c>
-      <c r="C9">
+      <c r="E8">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D9">
+        <v>7.1000000000000005E-5</v>
+      </c>
+      <c r="E9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D14">
         <v>3.6000000000000001E-5</v>
       </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B10">
-        <v>40</v>
-      </c>
-      <c r="C10">
+      <c r="E14">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D15">
+        <v>3.6000000000000001E-5</v>
+      </c>
+      <c r="E15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D16">
+        <v>3.6000000000000001E-5</v>
+      </c>
+      <c r="E16">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D17">
+        <v>3.6000000000000001E-5</v>
+      </c>
+      <c r="E17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="21" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="22" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D22">
+        <v>0</v>
+      </c>
+      <c r="E22">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D23">
+        <v>1.07E-4</v>
+      </c>
+      <c r="E23">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="26" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D26">
+        <v>1.07E-4</v>
+      </c>
+      <c r="E26">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="27" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D27">
         <v>7.1000000000000005E-5</v>
       </c>
-    </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>45</v>
-      </c>
-      <c r="C11">
+      <c r="E27">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D28">
         <v>7.1000000000000005E-5</v>
       </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>50</v>
-      </c>
-      <c r="C12">
-        <v>1.4300000000000001E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>55</v>
-      </c>
-      <c r="C13">
-        <v>1.07E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>60</v>
-      </c>
-      <c r="C14">
-        <v>1.7899999999999999E-4</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B15">
-        <v>65</v>
-      </c>
-      <c r="C15">
-        <v>2.5000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B16">
-        <v>70</v>
-      </c>
-      <c r="C16">
-        <v>1.7899999999999999E-4</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17">
-        <v>75</v>
-      </c>
-      <c r="C17">
-        <v>1.7899999999999999E-4</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18">
-        <v>80</v>
-      </c>
-      <c r="C18">
-        <v>4.2900000000000002E-4</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19">
-        <v>85</v>
-      </c>
-      <c r="C19">
-        <v>3.21E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20">
-        <v>90</v>
-      </c>
-      <c r="C20">
-        <v>5.0000000000000001E-4</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B21">
-        <v>95</v>
-      </c>
-      <c r="C21">
-        <v>3.9300000000000001E-4</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B22">
-        <v>100</v>
-      </c>
-      <c r="C22">
-        <v>6.7900000000000002E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B23">
-        <v>105</v>
-      </c>
-      <c r="C23">
-        <v>7.8600000000000002E-4</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B24">
-        <v>110</v>
-      </c>
-      <c r="C24">
-        <v>8.9300000000000002E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B25">
-        <v>115</v>
-      </c>
-      <c r="C25">
-        <v>1E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B26">
-        <v>120</v>
-      </c>
-      <c r="C26">
-        <v>1.0709999999999999E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B27">
-        <v>125</v>
-      </c>
-      <c r="C27">
-        <v>1.25E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B28">
-        <v>130</v>
-      </c>
-      <c r="C28">
-        <v>1.3209999999999999E-3</v>
+      <c r="E28">
+        <v>145</v>
       </c>
       <c r="J28" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B29">
-        <v>135</v>
-      </c>
-      <c r="C29">
-        <v>1.5709999999999999E-3</v>
+    <row r="29" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D29">
+        <v>7.1000000000000005E-5</v>
+      </c>
+      <c r="E29">
+        <v>150</v>
       </c>
       <c r="J29">
         <v>10</v>
@@ -4077,12 +4097,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B30">
-        <v>140</v>
-      </c>
-      <c r="C30">
-        <v>1.786E-3</v>
+    <row r="30" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D30">
+        <v>1.4300000000000001E-4</v>
+      </c>
+      <c r="E30">
+        <v>155</v>
       </c>
       <c r="J30">
         <v>30</v>
@@ -4091,12 +4111,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B31">
-        <v>145</v>
-      </c>
-      <c r="C31">
-        <v>2E-3</v>
+    <row r="31" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D31">
+        <v>1.7899999999999999E-4</v>
+      </c>
+      <c r="E31">
+        <v>160</v>
       </c>
       <c r="J31">
         <v>50</v>
@@ -4105,12 +4125,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B32">
-        <v>150</v>
-      </c>
-      <c r="C32">
-        <v>2.2859999999999998E-3</v>
+    <row r="32" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D32">
+        <v>3.6000000000000001E-5</v>
+      </c>
+      <c r="E32">
+        <v>165</v>
       </c>
       <c r="J32">
         <v>70</v>
@@ -4119,12 +4139,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B33">
-        <v>155</v>
-      </c>
-      <c r="C33">
-        <v>2.4290000000000002E-3</v>
+    <row r="33" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D33">
+        <v>7.1000000000000005E-5</v>
+      </c>
+      <c r="E33">
+        <v>170</v>
       </c>
       <c r="J33">
         <v>90</v>
@@ -4133,12 +4153,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B34">
-        <v>160</v>
-      </c>
-      <c r="C34">
-        <v>2.6069999999999999E-3</v>
+    <row r="34" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D34">
+        <v>1.7899999999999999E-4</v>
+      </c>
+      <c r="E34">
+        <v>175</v>
       </c>
       <c r="J34">
         <v>110</v>
@@ -4147,12 +4167,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B35">
-        <v>165</v>
-      </c>
-      <c r="C35">
-        <v>2.8570000000000002E-3</v>
+    <row r="35" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>180</v>
       </c>
       <c r="J35">
         <v>130</v>
@@ -4161,12 +4181,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B36">
-        <v>170</v>
-      </c>
-      <c r="C36">
-        <v>3.0360000000000001E-3</v>
+    <row r="36" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D36">
+        <v>2.14E-4</v>
+      </c>
+      <c r="E36">
+        <v>185</v>
       </c>
       <c r="J36">
         <v>150</v>
@@ -4175,12 +4195,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B37">
-        <v>175</v>
-      </c>
-      <c r="C37">
-        <v>3.107E-3</v>
+    <row r="37" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D37">
+        <v>1.7899999999999999E-4</v>
+      </c>
+      <c r="E37">
+        <v>190</v>
       </c>
       <c r="J37">
         <v>170</v>
@@ -4189,12 +4209,12 @@
         <v>0.107143</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B38">
-        <v>180</v>
-      </c>
-      <c r="C38">
-        <v>3.7859999999999999E-3</v>
+    <row r="38" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D38">
+        <v>2.14E-4</v>
+      </c>
+      <c r="E38">
+        <v>195</v>
       </c>
       <c r="J38">
         <v>190</v>
@@ -4203,12 +4223,12 @@
         <v>7.1429000000000006E-2</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B39">
-        <v>185</v>
-      </c>
-      <c r="C39">
-        <v>4.0000000000000001E-3</v>
+    <row r="39" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D39">
+        <v>1.7899999999999999E-4</v>
+      </c>
+      <c r="E39">
+        <v>200</v>
       </c>
       <c r="J39">
         <v>210</v>
@@ -4217,12 +4237,12 @@
         <v>7.1429000000000006E-2</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B40">
-        <v>190</v>
-      </c>
-      <c r="C40">
-        <v>4.3930000000000002E-3</v>
+    <row r="40" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>205</v>
       </c>
       <c r="J40">
         <v>230</v>
@@ -4231,12 +4251,12 @@
         <v>0.214286</v>
       </c>
     </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B41">
-        <v>195</v>
-      </c>
-      <c r="C41">
-        <v>4.4640000000000001E-3</v>
+    <row r="41" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D41">
+        <v>1.7899999999999999E-4</v>
+      </c>
+      <c r="E41">
+        <v>210</v>
       </c>
       <c r="J41">
         <v>250</v>
@@ -4245,12 +4265,12 @@
         <v>7.1429000000000006E-2</v>
       </c>
     </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B42">
-        <v>200</v>
-      </c>
-      <c r="C42">
-        <v>5.0000000000000001E-3</v>
+    <row r="42" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D42">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="E42">
+        <v>215</v>
       </c>
       <c r="J42">
         <v>270</v>
@@ -4259,12 +4279,12 @@
         <v>7.1429000000000006E-2</v>
       </c>
     </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B43">
-        <v>205</v>
-      </c>
-      <c r="C43">
-        <v>5.4289999999999998E-3</v>
+    <row r="43" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D43">
+        <v>1.7899999999999999E-4</v>
+      </c>
+      <c r="E43">
+        <v>220</v>
       </c>
       <c r="J43">
         <v>290</v>
@@ -4273,12 +4293,12 @@
         <v>0.107143</v>
       </c>
     </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B44">
-        <v>210</v>
-      </c>
-      <c r="C44">
-        <v>5.7860000000000003E-3</v>
+    <row r="44" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D44">
+        <v>2.8600000000000001E-4</v>
+      </c>
+      <c r="E44">
+        <v>225</v>
       </c>
       <c r="J44">
         <v>310</v>
@@ -4287,12 +4307,12 @@
         <v>0.17857100000000001</v>
       </c>
     </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B45">
-        <v>215</v>
-      </c>
-      <c r="C45">
-        <v>6.2139999999999999E-3</v>
+    <row r="45" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D45">
+        <v>2.8600000000000001E-4</v>
+      </c>
+      <c r="E45">
+        <v>230</v>
       </c>
       <c r="J45">
         <v>330</v>
@@ -4301,12 +4321,12 @@
         <v>0.32142900000000002</v>
       </c>
     </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B46">
-        <v>220</v>
-      </c>
-      <c r="C46">
-        <v>6.8929999999999998E-3</v>
+    <row r="46" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D46">
+        <v>1.4300000000000001E-4</v>
+      </c>
+      <c r="E46">
+        <v>235</v>
       </c>
       <c r="J46">
         <v>350</v>
@@ -4315,12 +4335,12 @@
         <v>0.28571400000000002</v>
       </c>
     </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B47">
-        <v>225</v>
-      </c>
-      <c r="C47">
-        <v>7.0359999999999997E-3</v>
+    <row r="47" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D47">
+        <v>2.14E-4</v>
+      </c>
+      <c r="E47">
+        <v>240</v>
       </c>
       <c r="J47">
         <v>370</v>
@@ -4329,12 +4349,12 @@
         <v>0.35714299999999999</v>
       </c>
     </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B48">
-        <v>230</v>
-      </c>
-      <c r="C48">
-        <v>7.4640000000000001E-3</v>
+    <row r="48" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D48">
+        <v>2.8600000000000001E-4</v>
+      </c>
+      <c r="E48">
+        <v>245</v>
       </c>
       <c r="J48">
         <v>390</v>
@@ -4343,12 +4363,12 @@
         <v>0.32142900000000002</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B49">
-        <v>235</v>
-      </c>
-      <c r="C49">
-        <v>8.0000000000000002E-3</v>
+    <row r="49" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D49">
+        <v>3.21E-4</v>
+      </c>
+      <c r="E49">
+        <v>250</v>
       </c>
       <c r="J49">
         <v>410</v>
@@ -4357,12 +4377,12 @@
         <v>0.57142899999999996</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B50">
-        <v>240</v>
-      </c>
-      <c r="C50">
-        <v>8.6070000000000001E-3</v>
+    <row r="50" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D50">
+        <v>2.8600000000000001E-4</v>
+      </c>
+      <c r="E50">
+        <v>255</v>
       </c>
       <c r="J50">
         <v>430</v>
@@ -4371,12 +4391,12 @@
         <v>0.46428599999999998</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B51">
-        <v>245</v>
-      </c>
-      <c r="C51">
-        <v>8.9999999999999993E-3</v>
+    <row r="51" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D51">
+        <v>3.57E-4</v>
+      </c>
+      <c r="E51">
+        <v>260</v>
       </c>
       <c r="J51">
         <v>450</v>
@@ -4385,12 +4405,12 @@
         <v>0.53571400000000002</v>
       </c>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B52">
-        <v>250</v>
-      </c>
-      <c r="C52">
-        <v>9.6430000000000005E-3</v>
+    <row r="52" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D52">
+        <v>2.14E-4</v>
+      </c>
+      <c r="E52">
+        <v>265</v>
       </c>
       <c r="J52">
         <v>470</v>
@@ -4399,12 +4419,12 @@
         <v>0.39285700000000001</v>
       </c>
     </row>
-    <row r="53" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B53">
-        <v>255</v>
-      </c>
-      <c r="C53">
-        <v>1.0142999999999999E-2</v>
+    <row r="53" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D53">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E53">
+        <v>270</v>
       </c>
       <c r="J53">
         <v>490</v>
@@ -4413,12 +4433,12 @@
         <v>0.57142899999999996</v>
       </c>
     </row>
-    <row r="54" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B54">
-        <v>260</v>
-      </c>
-      <c r="C54">
-        <v>1.0678999999999999E-2</v>
+    <row r="54" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D54">
+        <v>2.8600000000000001E-4</v>
+      </c>
+      <c r="E54">
+        <v>275</v>
       </c>
       <c r="J54">
         <v>510</v>
@@ -4427,12 +4447,12 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B55">
-        <v>265</v>
-      </c>
-      <c r="C55">
-        <v>1.1285999999999999E-2</v>
+    <row r="55" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D55">
+        <v>5.71E-4</v>
+      </c>
+      <c r="E55">
+        <v>280</v>
       </c>
       <c r="J55">
         <v>530</v>
@@ -4441,12 +4461,12 @@
         <v>0.42857099999999998</v>
       </c>
     </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B56">
-        <v>270</v>
-      </c>
-      <c r="C56">
-        <v>1.1964000000000001E-2</v>
+    <row r="56" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D56">
+        <v>2.5000000000000001E-4</v>
+      </c>
+      <c r="E56">
+        <v>285</v>
       </c>
       <c r="J56">
         <v>550</v>
@@ -4455,12 +4475,12 @@
         <v>0.57142899999999996</v>
       </c>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B57">
-        <v>275</v>
-      </c>
-      <c r="C57">
-        <v>1.2678999999999999E-2</v>
+    <row r="57" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D57">
+        <v>5.71E-4</v>
+      </c>
+      <c r="E57">
+        <v>290</v>
       </c>
       <c r="J57">
         <v>570</v>
@@ -4469,12 +4489,12 @@
         <v>0.71428599999999998</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B58">
-        <v>280</v>
-      </c>
-      <c r="C58">
-        <v>1.3285999999999999E-2</v>
+    <row r="58" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D58">
+        <v>4.2900000000000002E-4</v>
+      </c>
+      <c r="E58">
+        <v>295</v>
       </c>
       <c r="J58">
         <v>590</v>
@@ -4483,12 +4503,12 @@
         <v>0.82142899999999996</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B59">
-        <v>285</v>
-      </c>
-      <c r="C59">
-        <v>1.4071E-2</v>
+    <row r="59" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D59">
+        <v>2.14E-4</v>
+      </c>
+      <c r="E59">
+        <v>300</v>
       </c>
       <c r="J59">
         <v>610</v>
@@ -4497,12 +4517,12 @@
         <v>0.96428599999999998</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B60">
-        <v>290</v>
-      </c>
-      <c r="C60">
-        <v>1.4321E-2</v>
+    <row r="60" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D60">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E60">
+        <v>305</v>
       </c>
       <c r="J60">
         <v>630</v>
@@ -4511,12 +4531,12 @@
         <v>0.89285700000000001</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B61">
-        <v>295</v>
-      </c>
-      <c r="C61">
-        <v>1.5535999999999999E-2</v>
+    <row r="61" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D61">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="E61">
+        <v>310</v>
       </c>
       <c r="J61">
         <v>650</v>
@@ -4525,12 +4545,12 @@
         <v>0.96428599999999998</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B62">
-        <v>300</v>
-      </c>
-      <c r="C62">
-        <v>1.6463999999999999E-2</v>
+    <row r="62" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D62">
+        <v>5.0000000000000001E-4</v>
+      </c>
+      <c r="E62">
+        <v>315</v>
       </c>
       <c r="J62">
         <v>670</v>
@@ -4539,12 +4559,12 @@
         <v>0.96428599999999998</v>
       </c>
     </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B63">
-        <v>305</v>
-      </c>
-      <c r="C63">
-        <v>1.7107000000000001E-2</v>
+    <row r="63" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D63">
+        <v>4.2900000000000002E-4</v>
+      </c>
+      <c r="E63">
+        <v>320</v>
       </c>
       <c r="J63">
         <v>690</v>
@@ -4553,12 +4573,12 @@
         <v>1.035714</v>
       </c>
     </row>
-    <row r="64" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B64">
-        <v>310</v>
-      </c>
-      <c r="C64">
-        <v>1.8107000000000002E-2</v>
+    <row r="64" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D64">
+        <v>5.3600000000000002E-4</v>
+      </c>
+      <c r="E64">
+        <v>325</v>
       </c>
       <c r="J64">
         <v>710</v>
@@ -4567,12 +4587,12 @@
         <v>1.071429</v>
       </c>
     </row>
-    <row r="65" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B65">
-        <v>315</v>
-      </c>
-      <c r="C65">
-        <v>1.8643E-2</v>
+    <row r="65" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D65">
+        <v>7.8600000000000002E-4</v>
+      </c>
+      <c r="E65">
+        <v>330</v>
       </c>
       <c r="J65">
         <v>730</v>
@@ -4581,12 +4601,12 @@
         <v>1.071429</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B66">
-        <v>320</v>
-      </c>
-      <c r="C66">
-        <v>1.9963999999999999E-2</v>
+    <row r="66" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D66">
+        <v>5.3600000000000002E-4</v>
+      </c>
+      <c r="E66">
+        <v>335</v>
       </c>
       <c r="J66">
         <v>750</v>
@@ -4595,12 +4615,12 @@
         <v>1.214286</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B67">
-        <v>325</v>
-      </c>
-      <c r="C67">
-        <v>2.0607E-2</v>
+    <row r="67" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D67">
+        <v>6.7900000000000002E-4</v>
+      </c>
+      <c r="E67">
+        <v>340</v>
       </c>
       <c r="J67">
         <v>770</v>
@@ -4609,12 +4629,12 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B68">
-        <v>330</v>
-      </c>
-      <c r="C68">
-        <v>2.1714000000000001E-2</v>
+    <row r="68" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D68">
+        <v>6.7900000000000002E-4</v>
+      </c>
+      <c r="E68">
+        <v>345</v>
       </c>
       <c r="J68">
         <v>790</v>
@@ -4623,12 +4643,12 @@
         <v>1.321429</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B69">
-        <v>335</v>
-      </c>
-      <c r="C69">
-        <v>2.2536E-2</v>
+    <row r="69" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D69">
+        <v>7.1400000000000001E-4</v>
+      </c>
+      <c r="E69">
+        <v>350</v>
       </c>
       <c r="J69">
         <v>810</v>
@@ -4637,12 +4657,12 @@
         <v>1.357143</v>
       </c>
     </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B70">
-        <v>340</v>
-      </c>
-      <c r="C70">
-        <v>2.3643000000000001E-2</v>
+    <row r="70" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D70">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="E70">
+        <v>355</v>
       </c>
       <c r="J70">
         <v>830</v>
@@ -4651,12 +4671,12 @@
         <v>1.428571</v>
       </c>
     </row>
-    <row r="71" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B71">
-        <v>345</v>
-      </c>
-      <c r="C71">
-        <v>2.4535999999999999E-2</v>
+    <row r="71" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D71">
+        <v>5.71E-4</v>
+      </c>
+      <c r="E71">
+        <v>360</v>
       </c>
       <c r="J71">
         <v>850</v>
@@ -4665,12 +4685,12 @@
         <v>1.464286</v>
       </c>
     </row>
-    <row r="72" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B72">
-        <v>350</v>
-      </c>
-      <c r="C72">
-        <v>2.5786E-2</v>
+    <row r="72" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D72">
+        <v>8.5700000000000001E-4</v>
+      </c>
+      <c r="E72">
+        <v>365</v>
       </c>
       <c r="J72">
         <v>870</v>
@@ -4679,12 +4699,12 @@
         <v>1.785714</v>
       </c>
     </row>
-    <row r="73" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B73">
-        <v>355</v>
-      </c>
-      <c r="C73">
-        <v>2.6856999999999999E-2</v>
+    <row r="73" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D73">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="E73">
+        <v>370</v>
       </c>
       <c r="J73">
         <v>890</v>
@@ -4693,12 +4713,12 @@
         <v>1.714286</v>
       </c>
     </row>
-    <row r="74" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B74">
-        <v>360</v>
-      </c>
-      <c r="C74">
-        <v>2.8035999999999998E-2</v>
+    <row r="74" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D74">
+        <v>7.1400000000000001E-4</v>
+      </c>
+      <c r="E74">
+        <v>375</v>
       </c>
       <c r="J74">
         <v>910</v>
@@ -4707,12 +4727,12 @@
         <v>1.892857</v>
       </c>
     </row>
-    <row r="75" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B75">
-        <v>365</v>
-      </c>
-      <c r="C75">
-        <v>2.9749999999999999E-2</v>
+    <row r="75" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D75">
+        <v>7.5000000000000002E-4</v>
+      </c>
+      <c r="E75">
+        <v>380</v>
       </c>
       <c r="J75">
         <v>930</v>
@@ -4721,12 +4741,12 @@
         <v>1.857143</v>
       </c>
     </row>
-    <row r="76" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B76">
-        <v>370</v>
-      </c>
-      <c r="C76">
-        <v>3.0321000000000001E-2</v>
+    <row r="76" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D76">
+        <v>9.2900000000000003E-4</v>
+      </c>
+      <c r="E76">
+        <v>385</v>
       </c>
       <c r="J76">
         <v>950</v>
@@ -4735,12 +4755,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B77">
-        <v>375</v>
-      </c>
-      <c r="C77">
-        <v>3.1928999999999999E-2</v>
+    <row r="77" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D77">
+        <v>7.8600000000000002E-4</v>
+      </c>
+      <c r="E77">
+        <v>390</v>
       </c>
       <c r="J77">
         <v>970</v>
@@ -4749,12 +4769,12 @@
         <v>2.0714290000000002</v>
       </c>
     </row>
-    <row r="78" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B78">
-        <v>380</v>
-      </c>
-      <c r="C78">
-        <v>3.3429E-2</v>
+    <row r="78" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D78">
+        <v>8.9300000000000002E-4</v>
+      </c>
+      <c r="E78">
+        <v>395</v>
       </c>
       <c r="J78">
         <v>990</v>
@@ -4763,996 +4783,972 @@
         <v>2.1071430000000002</v>
       </c>
     </row>
-    <row r="79" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B79">
-        <v>385</v>
-      </c>
-      <c r="C79">
-        <v>3.4679000000000001E-2</v>
-      </c>
-    </row>
-    <row r="80" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B80">
-        <v>390</v>
-      </c>
-      <c r="C80">
-        <v>3.5785999999999998E-2</v>
-      </c>
-    </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B81">
-        <v>395</v>
-      </c>
-      <c r="C81">
-        <v>3.6679000000000003E-2</v>
-      </c>
-    </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B82">
+    <row r="79" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D79">
+        <v>8.2100000000000001E-4</v>
+      </c>
+      <c r="E79">
         <v>400</v>
       </c>
-      <c r="C82">
-        <v>3.8071000000000001E-2</v>
-      </c>
-    </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B83">
+    </row>
+    <row r="80" spans="4:11" x14ac:dyDescent="0.3">
+      <c r="D80">
+        <v>9.6400000000000001E-4</v>
+      </c>
+      <c r="E80">
         <v>405</v>
       </c>
-      <c r="C83">
-        <v>3.9607000000000003E-2</v>
-      </c>
-    </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B84">
+    </row>
+    <row r="81" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D81">
+        <v>8.2100000000000001E-4</v>
+      </c>
+      <c r="E81">
         <v>410</v>
       </c>
-      <c r="C84">
-        <v>4.0856999999999997E-2</v>
-      </c>
-    </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B85">
+    </row>
+    <row r="82" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D82">
+        <v>9.2900000000000003E-4</v>
+      </c>
+      <c r="E82">
         <v>415</v>
       </c>
-      <c r="C85">
-        <v>4.2606999999999999E-2</v>
-      </c>
-    </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B86">
+    </row>
+    <row r="83" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D83">
+        <v>8.9300000000000002E-4</v>
+      </c>
+      <c r="E83">
         <v>420</v>
       </c>
-      <c r="C86">
-        <v>4.4249999999999998E-2</v>
-      </c>
-    </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B87">
+    </row>
+    <row r="84" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D84">
+        <v>9.6400000000000001E-4</v>
+      </c>
+      <c r="E84">
         <v>425</v>
       </c>
-      <c r="C87">
-        <v>4.5678999999999997E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B88">
+    </row>
+    <row r="85" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D85">
+        <v>9.6400000000000001E-4</v>
+      </c>
+      <c r="E85">
         <v>430</v>
       </c>
-      <c r="C88">
-        <v>4.7071000000000002E-2</v>
-      </c>
-    </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B89">
+    </row>
+    <row r="86" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D86">
+        <v>1E-3</v>
+      </c>
+      <c r="E86">
         <v>435</v>
       </c>
-      <c r="C89">
-        <v>4.9070999999999997E-2</v>
-      </c>
-    </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B90">
+    </row>
+    <row r="87" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D87">
+        <v>1E-3</v>
+      </c>
+      <c r="E87">
         <v>440</v>
       </c>
-      <c r="C90">
-        <v>5.0285999999999997E-2</v>
-      </c>
-    </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B91">
+    </row>
+    <row r="88" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D88">
+        <v>1.1429999999999999E-3</v>
+      </c>
+      <c r="E88">
         <v>445</v>
       </c>
-      <c r="C91">
-        <v>5.2357000000000001E-2</v>
-      </c>
-    </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B92">
+    </row>
+    <row r="89" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D89">
+        <v>1E-3</v>
+      </c>
+      <c r="E89">
         <v>450</v>
       </c>
-      <c r="C92">
-        <v>5.3928999999999998E-2</v>
-      </c>
-    </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B93">
+    </row>
+    <row r="90" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D90">
+        <v>1.036E-3</v>
+      </c>
+      <c r="E90">
         <v>455</v>
       </c>
-      <c r="C93">
-        <v>5.6000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B94">
+    </row>
+    <row r="91" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D91">
+        <v>1.1069999999999999E-3</v>
+      </c>
+      <c r="E91">
         <v>460</v>
       </c>
-      <c r="C94">
-        <v>5.7964000000000002E-2</v>
-      </c>
-    </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B95">
+    </row>
+    <row r="92" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D92">
+        <v>1.1069999999999999E-3</v>
+      </c>
+      <c r="E92">
         <v>465</v>
       </c>
-      <c r="C95">
-        <v>5.9464000000000003E-2</v>
-      </c>
-    </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B96">
+    </row>
+    <row r="93" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D93">
+        <v>1.1789999999999999E-3</v>
+      </c>
+      <c r="E93">
         <v>470</v>
       </c>
-      <c r="C96">
-        <v>6.1607000000000002E-2</v>
-      </c>
-    </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B97">
+    </row>
+    <row r="94" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D94">
+        <v>1.1429999999999999E-3</v>
+      </c>
+      <c r="E94">
         <v>475</v>
       </c>
-      <c r="C97">
-        <v>6.3535999999999995E-2</v>
-      </c>
-    </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B98">
+    </row>
+    <row r="95" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D95">
+        <v>1E-3</v>
+      </c>
+      <c r="E95">
         <v>480</v>
       </c>
-      <c r="C98">
-        <v>6.5679000000000001E-2</v>
-      </c>
-    </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B99">
+    </row>
+    <row r="96" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D96">
+        <v>1.0709999999999999E-3</v>
+      </c>
+      <c r="E96">
         <v>485</v>
       </c>
-      <c r="C99">
-        <v>6.7785999999999999E-2</v>
-      </c>
-    </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B100">
+    </row>
+    <row r="97" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D97">
+        <v>1.3569999999999999E-3</v>
+      </c>
+      <c r="E97">
         <v>490</v>
       </c>
-      <c r="C100">
-        <v>6.9642999999999997E-2</v>
-      </c>
-    </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B101">
+    </row>
+    <row r="98" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D98">
+        <v>1.214E-3</v>
+      </c>
+      <c r="E98">
         <v>495</v>
       </c>
-      <c r="C101">
-        <v>7.1714E-2</v>
-      </c>
-    </row>
-    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B102">
+    </row>
+    <row r="99" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D99">
+        <v>1.286E-3</v>
+      </c>
+      <c r="E99">
         <v>500</v>
       </c>
-      <c r="C102">
-        <v>7.5036000000000005E-2</v>
-      </c>
-    </row>
-    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B103">
+    </row>
+    <row r="100" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D100">
+        <v>1.3209999999999999E-3</v>
+      </c>
+      <c r="E100">
         <v>505</v>
       </c>
-      <c r="C103">
-        <v>7.8E-2</v>
-      </c>
-    </row>
-    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B104">
+    </row>
+    <row r="101" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D101">
+        <v>1.464E-3</v>
+      </c>
+      <c r="E101">
         <v>510</v>
       </c>
-      <c r="C104">
-        <v>7.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="105" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B105">
+    </row>
+    <row r="102" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D102">
+        <v>1.464E-3</v>
+      </c>
+      <c r="E102">
         <v>515</v>
       </c>
-      <c r="C105">
-        <v>8.0679000000000001E-2</v>
-      </c>
-    </row>
-    <row r="106" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B106">
+    </row>
+    <row r="103" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D103">
+        <v>1.3209999999999999E-3</v>
+      </c>
+      <c r="E103">
         <v>520</v>
       </c>
-      <c r="C106">
-        <v>8.2392999999999994E-2</v>
-      </c>
-    </row>
-    <row r="107" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B107">
+    </row>
+    <row r="104" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D104">
+        <v>1.464E-3</v>
+      </c>
+      <c r="E104">
         <v>525</v>
       </c>
-      <c r="C107">
-        <v>8.5142999999999996E-2</v>
-      </c>
-    </row>
-    <row r="108" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B108">
+    </row>
+    <row r="105" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D105">
+        <v>1.286E-3</v>
+      </c>
+      <c r="E105">
         <v>530</v>
       </c>
-      <c r="C108">
-        <v>8.7320999999999996E-2</v>
-      </c>
-    </row>
-    <row r="109" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B109">
+    </row>
+    <row r="106" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D106">
+        <v>1.536E-3</v>
+      </c>
+      <c r="E106">
         <v>535</v>
       </c>
-      <c r="C109">
-        <v>9.0428999999999995E-2</v>
-      </c>
-    </row>
-    <row r="110" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B110">
+    </row>
+    <row r="107" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D107">
+        <v>1.5E-3</v>
+      </c>
+      <c r="E107">
         <v>540</v>
       </c>
-      <c r="C110">
-        <v>9.2964000000000005E-2</v>
-      </c>
-    </row>
-    <row r="111" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B111">
+    </row>
+    <row r="108" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D108">
+        <v>1.6069999999999999E-3</v>
+      </c>
+      <c r="E108">
         <v>545</v>
       </c>
-      <c r="C111">
-        <v>9.5143000000000005E-2</v>
-      </c>
-    </row>
-    <row r="112" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B112">
+    </row>
+    <row r="109" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D109">
+        <v>1.536E-3</v>
+      </c>
+      <c r="E109">
         <v>550</v>
       </c>
-      <c r="C112">
-        <v>9.7606999999999999E-2</v>
-      </c>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B113">
+    </row>
+    <row r="110" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D110">
+        <v>1.464E-3</v>
+      </c>
+      <c r="E110">
         <v>555</v>
       </c>
-      <c r="C113">
-        <v>0.100643</v>
-      </c>
-    </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B114">
+    </row>
+    <row r="111" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D111">
+        <v>1.464E-3</v>
+      </c>
+      <c r="E111">
         <v>560</v>
       </c>
-      <c r="C114">
-        <v>0.103786</v>
-      </c>
-    </row>
-    <row r="115" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B115">
+    </row>
+    <row r="112" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D112">
+        <v>1.5709999999999999E-3</v>
+      </c>
+      <c r="E112">
         <v>565</v>
       </c>
-      <c r="C115">
-        <v>0.10610700000000001</v>
-      </c>
-    </row>
-    <row r="116" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B116">
+    </row>
+    <row r="113" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D113">
+        <v>1.8209999999999999E-3</v>
+      </c>
+      <c r="E113">
         <v>570</v>
       </c>
-      <c r="C116">
-        <v>0.10878599999999999</v>
-      </c>
-    </row>
-    <row r="117" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B117">
+    </row>
+    <row r="114" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D114">
+        <v>1.6069999999999999E-3</v>
+      </c>
+      <c r="E114">
         <v>575</v>
       </c>
-      <c r="C117">
-        <v>0.11264299999999999</v>
-      </c>
-    </row>
-    <row r="118" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B118">
+    </row>
+    <row r="115" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D115">
+        <v>1.786E-3</v>
+      </c>
+      <c r="E115">
         <v>580</v>
       </c>
-      <c r="C118">
-        <v>0.115857</v>
-      </c>
-    </row>
-    <row r="119" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B119">
+    </row>
+    <row r="116" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D116">
+        <v>1.75E-3</v>
+      </c>
+      <c r="E116">
         <v>585</v>
       </c>
-      <c r="C119">
-        <v>0.117643</v>
-      </c>
-    </row>
-    <row r="120" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B120">
+    </row>
+    <row r="117" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D117">
+        <v>1.8209999999999999E-3</v>
+      </c>
+      <c r="E117">
         <v>590</v>
       </c>
-      <c r="C120">
-        <v>0.12042899999999999</v>
-      </c>
-    </row>
-    <row r="121" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B121">
+    </row>
+    <row r="118" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D118">
+        <v>1.9289999999999999E-3</v>
+      </c>
+      <c r="E118">
         <v>595</v>
       </c>
-      <c r="C121">
-        <v>0.12385699999999999</v>
-      </c>
-    </row>
-    <row r="122" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B122">
+    </row>
+    <row r="119" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D119">
+        <v>1.8569999999999999E-3</v>
+      </c>
+      <c r="E119">
         <v>600</v>
       </c>
-      <c r="C122">
-        <v>0.12671399999999999</v>
-      </c>
-    </row>
-    <row r="123" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B123">
+    </row>
+    <row r="120" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D120">
+        <v>1.964E-3</v>
+      </c>
+      <c r="E120">
         <v>605</v>
       </c>
-      <c r="C123">
-        <v>0.130107</v>
-      </c>
-    </row>
-    <row r="124" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B124">
+    </row>
+    <row r="121" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D121">
+        <v>1.964E-3</v>
+      </c>
+      <c r="E121">
         <v>610</v>
       </c>
-      <c r="C124">
-        <v>0.13292899999999999</v>
-      </c>
-    </row>
-    <row r="125" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B125">
+    </row>
+    <row r="122" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D122">
+        <v>1.8929999999999999E-3</v>
+      </c>
+      <c r="E122">
         <v>615</v>
       </c>
-      <c r="C125">
-        <v>0.136714</v>
-      </c>
-    </row>
-    <row r="126" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B126">
+    </row>
+    <row r="123" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D123">
+        <v>2.036E-3</v>
+      </c>
+      <c r="E123">
         <v>620</v>
       </c>
-      <c r="C126">
-        <v>0.139821</v>
-      </c>
-    </row>
-    <row r="127" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B127">
+    </row>
+    <row r="124" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D124">
+        <v>1.964E-3</v>
+      </c>
+      <c r="E124">
         <v>625</v>
       </c>
-      <c r="C127">
-        <v>0.14496400000000001</v>
-      </c>
-    </row>
-    <row r="128" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B128">
+    </row>
+    <row r="125" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D125">
+        <v>2.036E-3</v>
+      </c>
+      <c r="E125">
         <v>630</v>
       </c>
-      <c r="C128">
-        <v>0.14660699999999999</v>
-      </c>
-    </row>
-    <row r="129" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B129">
+    </row>
+    <row r="126" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D126">
+        <v>2.036E-3</v>
+      </c>
+      <c r="E126">
         <v>635</v>
       </c>
-      <c r="C129">
-        <v>0.15346399999999999</v>
-      </c>
-    </row>
-    <row r="130" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B130">
+    </row>
+    <row r="127" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D127">
+        <v>2E-3</v>
+      </c>
+      <c r="E127">
         <v>640</v>
       </c>
-      <c r="C130">
-        <v>0.15378600000000001</v>
-      </c>
-    </row>
-    <row r="131" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B131">
+    </row>
+    <row r="128" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D128">
+        <v>2.0709999999999999E-3</v>
+      </c>
+      <c r="E128">
         <v>645</v>
       </c>
-      <c r="C131">
-        <v>0.157357</v>
-      </c>
-    </row>
-    <row r="132" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B132">
+    </row>
+    <row r="129" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D129">
+        <v>2.1429999999999999E-3</v>
+      </c>
+      <c r="E129">
         <v>650</v>
       </c>
-      <c r="C132">
-        <v>0.160714</v>
-      </c>
-    </row>
-    <row r="133" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B133">
+    </row>
+    <row r="130" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D130">
+        <v>2.2139999999999998E-3</v>
+      </c>
+      <c r="E130">
         <v>655</v>
       </c>
-      <c r="C133">
-        <v>0.16492899999999999</v>
-      </c>
-    </row>
-    <row r="134" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B134">
+    </row>
+    <row r="131" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D131">
+        <v>2.1429999999999999E-3</v>
+      </c>
+      <c r="E131">
         <v>660</v>
       </c>
-      <c r="C134">
-        <v>0.167821</v>
-      </c>
-    </row>
-    <row r="135" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B135">
+    </row>
+    <row r="132" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D132">
+        <v>2.1789999999999999E-3</v>
+      </c>
+      <c r="E132">
         <v>665</v>
       </c>
-      <c r="C135">
-        <v>0.172571</v>
-      </c>
-    </row>
-    <row r="136" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B136">
+    </row>
+    <row r="133" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D133">
+        <v>2.2139999999999998E-3</v>
+      </c>
+      <c r="E133">
         <v>670</v>
       </c>
-      <c r="C136">
-        <v>0.17582100000000001</v>
-      </c>
-    </row>
-    <row r="137" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B137">
+    </row>
+    <row r="134" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D134">
+        <v>2.2859999999999998E-3</v>
+      </c>
+      <c r="E134">
         <v>675</v>
       </c>
-      <c r="C137">
-        <v>0.18010699999999999</v>
-      </c>
-    </row>
-    <row r="138" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B138">
+    </row>
+    <row r="135" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D135">
+        <v>2.3210000000000001E-3</v>
+      </c>
+      <c r="E135">
         <v>680</v>
       </c>
-      <c r="C138">
-        <v>0.18671399999999999</v>
-      </c>
-    </row>
-    <row r="139" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B139">
+    </row>
+    <row r="136" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D136">
+        <v>2.3930000000000002E-3</v>
+      </c>
+      <c r="E136">
         <v>685</v>
       </c>
-      <c r="C139">
-        <v>0.18792900000000001</v>
-      </c>
-    </row>
-    <row r="140" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B140">
+    </row>
+    <row r="137" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D137">
+        <v>2.464E-3</v>
+      </c>
+      <c r="E137">
         <v>690</v>
       </c>
-      <c r="C140">
-        <v>0.19214300000000001</v>
-      </c>
-    </row>
-    <row r="141" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B141">
+    </row>
+    <row r="138" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D138">
+        <v>2.464E-3</v>
+      </c>
+      <c r="E138">
         <v>695</v>
       </c>
-      <c r="C141">
-        <v>0.19717899999999999</v>
-      </c>
-    </row>
-    <row r="142" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B142">
+    </row>
+    <row r="139" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D139">
+        <v>2.3570000000000002E-3</v>
+      </c>
+      <c r="E139">
         <v>700</v>
       </c>
-      <c r="C142">
-        <v>0.200321</v>
-      </c>
-    </row>
-    <row r="143" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B143">
+    </row>
+    <row r="140" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D140">
+        <v>2.5360000000000001E-3</v>
+      </c>
+      <c r="E140">
         <v>705</v>
       </c>
-      <c r="C143">
-        <v>0.20474999999999999</v>
-      </c>
-    </row>
-    <row r="144" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B144">
+    </row>
+    <row r="141" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D141">
+        <v>2.6069999999999999E-3</v>
+      </c>
+      <c r="E141">
         <v>710</v>
       </c>
-      <c r="C144">
-        <v>0.20921400000000001</v>
-      </c>
-    </row>
-    <row r="145" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B145">
+    </row>
+    <row r="142" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D142">
+        <v>2.5360000000000001E-3</v>
+      </c>
+      <c r="E142">
         <v>715</v>
       </c>
-      <c r="C145">
-        <v>0.213536</v>
-      </c>
-    </row>
-    <row r="146" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B146">
+    </row>
+    <row r="143" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D143">
+        <v>2.6069999999999999E-3</v>
+      </c>
+      <c r="E143">
         <v>720</v>
       </c>
-      <c r="C146">
-        <v>0.22067899999999999</v>
-      </c>
-    </row>
-    <row r="147" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B147">
+    </row>
+    <row r="144" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D144">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="E144">
         <v>725</v>
       </c>
-      <c r="C147">
-        <v>0.22257099999999999</v>
-      </c>
-    </row>
-    <row r="148" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B148">
+    </row>
+    <row r="145" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D145">
+        <v>2.7139999999999998E-3</v>
+      </c>
+      <c r="E145">
         <v>730</v>
       </c>
-      <c r="C148">
-        <v>0.22657099999999999</v>
-      </c>
-    </row>
-    <row r="149" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B149">
+    </row>
+    <row r="146" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D146">
+        <v>2.643E-3</v>
+      </c>
+      <c r="E146">
         <v>735</v>
       </c>
-      <c r="C149">
-        <v>0.23153599999999999</v>
-      </c>
-    </row>
-    <row r="150" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B150">
+    </row>
+    <row r="147" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D147">
+        <v>2.679E-3</v>
+      </c>
+      <c r="E147">
         <v>740</v>
       </c>
-      <c r="C150">
-        <v>0.23646400000000001</v>
-      </c>
-    </row>
-    <row r="151" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B151">
+    </row>
+    <row r="148" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D148">
+        <v>2.9640000000000001E-3</v>
+      </c>
+      <c r="E148">
         <v>745</v>
       </c>
-      <c r="C151">
-        <v>0.24046400000000001</v>
-      </c>
-    </row>
-    <row r="152" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B152">
+    </row>
+    <row r="149" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D149">
+        <v>2.8930000000000002E-3</v>
+      </c>
+      <c r="E149">
         <v>750</v>
       </c>
-      <c r="C152">
-        <v>0.24621399999999999</v>
-      </c>
-    </row>
-    <row r="153" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B153">
+    </row>
+    <row r="150" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D150">
+        <v>2.8570000000000002E-3</v>
+      </c>
+      <c r="E150">
         <v>755</v>
       </c>
-      <c r="C153">
-        <v>0.25432100000000002</v>
-      </c>
-    </row>
-    <row r="154" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B154">
+    </row>
+    <row r="151" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D151">
+        <v>2.9290000000000002E-3</v>
+      </c>
+      <c r="E151">
         <v>760</v>
       </c>
-      <c r="C154">
-        <v>0.25567899999999999</v>
-      </c>
-    </row>
-    <row r="155" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B155">
+    </row>
+    <row r="152" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D152">
+        <v>2.9290000000000002E-3</v>
+      </c>
+      <c r="E152">
         <v>765</v>
       </c>
-      <c r="C155">
-        <v>0.26035700000000001</v>
-      </c>
-    </row>
-    <row r="156" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B156">
+    </row>
+    <row r="153" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D153">
+        <v>2.9290000000000002E-3</v>
+      </c>
+      <c r="E153">
         <v>770</v>
       </c>
-      <c r="C156">
-        <v>0.26589299999999999</v>
-      </c>
-    </row>
-    <row r="157" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B157">
+    </row>
+    <row r="154" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D154">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E154">
         <v>775</v>
       </c>
-      <c r="C157">
-        <v>0.27232099999999998</v>
-      </c>
-    </row>
-    <row r="158" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B158">
+    </row>
+    <row r="155" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D155">
+        <v>3.0709999999999999E-3</v>
+      </c>
+      <c r="E155">
         <v>780</v>
       </c>
-      <c r="C158">
-        <v>0.27746399999999999</v>
-      </c>
-    </row>
-    <row r="159" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B159">
+    </row>
+    <row r="156" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D156">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E156">
         <v>785</v>
       </c>
-      <c r="C159">
-        <v>0.28499999999999998</v>
-      </c>
-    </row>
-    <row r="160" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B160">
+    </row>
+    <row r="157" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D157">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="E157">
         <v>790</v>
       </c>
-      <c r="C160">
-        <v>0.28849999999999998</v>
-      </c>
-    </row>
-    <row r="161" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B161">
+    </row>
+    <row r="158" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D158">
+        <v>3.143E-3</v>
+      </c>
+      <c r="E158">
         <v>795</v>
       </c>
-      <c r="C161">
-        <v>0.29328599999999999</v>
-      </c>
-    </row>
-    <row r="162" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B162">
+    </row>
+    <row r="159" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D159">
+        <v>3.0360000000000001E-3</v>
+      </c>
+      <c r="E159">
         <v>800</v>
       </c>
-      <c r="C162">
-        <v>0.29807099999999997</v>
-      </c>
-    </row>
-    <row r="163" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B163">
+    </row>
+    <row r="160" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D160">
+        <v>3.2859999999999999E-3</v>
+      </c>
+      <c r="E160">
         <v>805</v>
       </c>
-      <c r="C163">
-        <v>0.30396400000000001</v>
-      </c>
-    </row>
-    <row r="164" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B164">
+    </row>
+    <row r="161" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D161">
+        <v>3.2859999999999999E-3</v>
+      </c>
+      <c r="E161">
         <v>810</v>
       </c>
-      <c r="C164">
-        <v>0.30917899999999998</v>
-      </c>
-    </row>
-    <row r="165" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B165">
+    </row>
+    <row r="162" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D162">
+        <v>3.143E-3</v>
+      </c>
+      <c r="E162">
         <v>815</v>
       </c>
-      <c r="C165">
-        <v>0.31896400000000003</v>
-      </c>
-    </row>
-    <row r="166" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B166">
+    </row>
+    <row r="163" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D163">
+        <v>3.2499999999999999E-3</v>
+      </c>
+      <c r="E163">
         <v>820</v>
       </c>
-      <c r="C166">
-        <v>0.32060699999999998</v>
-      </c>
-    </row>
-    <row r="167" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B167">
+    </row>
+    <row r="164" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D164">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="E164">
         <v>825</v>
       </c>
-      <c r="C167">
-        <v>0.32628600000000002</v>
-      </c>
-    </row>
-    <row r="168" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B168">
+    </row>
+    <row r="165" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D165">
+        <v>3.3930000000000002E-3</v>
+      </c>
+      <c r="E165">
         <v>830</v>
       </c>
-      <c r="C168">
-        <v>0.332536</v>
-      </c>
-    </row>
-    <row r="169" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B169">
+    </row>
+    <row r="166" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D166">
+        <v>3.571E-3</v>
+      </c>
+      <c r="E166">
         <v>835</v>
       </c>
-      <c r="C169">
-        <v>0.33774999999999999</v>
-      </c>
-    </row>
-    <row r="170" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B170">
+    </row>
+    <row r="167" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D167">
+        <v>3.5000000000000001E-3</v>
+      </c>
+      <c r="E167">
         <v>840</v>
       </c>
-      <c r="C170">
-        <v>0.34735700000000003</v>
-      </c>
-    </row>
-    <row r="171" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B171">
+    </row>
+    <row r="168" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D168">
+        <v>3.7499999999999999E-3</v>
+      </c>
+      <c r="E168">
         <v>845</v>
       </c>
-      <c r="C171">
-        <v>0.35057100000000002</v>
-      </c>
-    </row>
-    <row r="172" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B172">
+    </row>
+    <row r="169" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D169">
+        <v>3.679E-3</v>
+      </c>
+      <c r="E169">
         <v>850</v>
       </c>
-      <c r="C172">
-        <v>0.35760700000000001</v>
-      </c>
-    </row>
-    <row r="173" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B173">
+    </row>
+    <row r="170" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D170">
+        <v>3.643E-3</v>
+      </c>
+      <c r="E170">
         <v>855</v>
       </c>
-      <c r="C173">
-        <v>0.36303600000000003</v>
-      </c>
-    </row>
-    <row r="174" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B174">
+    </row>
+    <row r="171" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D171">
+        <v>3.7859999999999999E-3</v>
+      </c>
+      <c r="E171">
         <v>860</v>
       </c>
-      <c r="C174">
-        <v>0.36932100000000001</v>
-      </c>
-    </row>
-    <row r="175" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B175">
+    </row>
+    <row r="172" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D172">
+        <v>3.9290000000000002E-3</v>
+      </c>
+      <c r="E172">
         <v>865</v>
       </c>
-      <c r="C175">
-        <v>0.38128600000000001</v>
-      </c>
-    </row>
-    <row r="176" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B176">
+    </row>
+    <row r="173" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D173">
+        <v>3.8930000000000002E-3</v>
+      </c>
+      <c r="E173">
         <v>870</v>
       </c>
-      <c r="C176">
-        <v>0.382714</v>
-      </c>
-    </row>
-    <row r="177" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B177">
+    </row>
+    <row r="174" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D174">
+        <v>3.7499999999999999E-3</v>
+      </c>
+      <c r="E174">
         <v>875</v>
       </c>
-      <c r="C177">
-        <v>0.38964300000000002</v>
-      </c>
-    </row>
-    <row r="178" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B178">
+    </row>
+    <row r="175" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D175">
+        <v>3.8930000000000002E-3</v>
+      </c>
+      <c r="E175">
         <v>880</v>
       </c>
-      <c r="C178">
-        <v>0.396393</v>
-      </c>
-    </row>
-    <row r="179" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B179">
+    </row>
+    <row r="176" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D176">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E176">
         <v>885</v>
       </c>
-      <c r="C179">
-        <v>0.40475</v>
-      </c>
-    </row>
-    <row r="180" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B180">
+    </row>
+    <row r="177" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D177">
+        <v>3.9639999999999996E-3</v>
+      </c>
+      <c r="E177">
         <v>890</v>
       </c>
-      <c r="C180">
-        <v>0.41092899999999999</v>
-      </c>
-    </row>
-    <row r="181" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B181">
+    </row>
+    <row r="178" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D178">
+        <v>4.0359999999999997E-3</v>
+      </c>
+      <c r="E178">
         <v>895</v>
       </c>
-      <c r="C181">
-        <v>0.416821</v>
-      </c>
-    </row>
-    <row r="182" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B182">
+    </row>
+    <row r="179" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D179">
+        <v>4.0000000000000001E-3</v>
+      </c>
+      <c r="E179">
         <v>900</v>
       </c>
-      <c r="C182">
-        <v>0.42285699999999998</v>
-      </c>
-    </row>
-    <row r="183" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B183">
+    </row>
+    <row r="180" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D180">
+        <v>4.2500000000000003E-3</v>
+      </c>
+      <c r="E180">
         <v>905</v>
       </c>
-      <c r="C183">
-        <v>0.43071399999999999</v>
-      </c>
-    </row>
-    <row r="184" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B184">
+    </row>
+    <row r="181" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D181">
+        <v>4.1070000000000004E-3</v>
+      </c>
+      <c r="E181">
         <v>910</v>
       </c>
-      <c r="C184">
-        <v>0.44132100000000002</v>
-      </c>
-    </row>
-    <row r="185" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B185">
+    </row>
+    <row r="182" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D182">
+        <v>4.1070000000000004E-3</v>
+      </c>
+      <c r="E182">
         <v>915</v>
       </c>
-      <c r="C185">
-        <v>0.44428600000000001</v>
-      </c>
-    </row>
-    <row r="186" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B186">
+    </row>
+    <row r="183" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D183">
+        <v>4.2139999999999999E-3</v>
+      </c>
+      <c r="E183">
         <v>920</v>
       </c>
-      <c r="C186">
-        <v>0.453679</v>
-      </c>
-    </row>
-    <row r="187" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B187">
+    </row>
+    <row r="184" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D184">
+        <v>4.3569999999999998E-3</v>
+      </c>
+      <c r="E184">
         <v>925</v>
       </c>
-      <c r="C187">
-        <v>0.45824999999999999</v>
-      </c>
-    </row>
-    <row r="188" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B188">
+    </row>
+    <row r="185" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D185">
+        <v>4.1790000000000004E-3</v>
+      </c>
+      <c r="E185">
         <v>930</v>
       </c>
-      <c r="C188">
-        <v>0.46850000000000003</v>
-      </c>
-    </row>
-    <row r="189" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B189">
+    </row>
+    <row r="186" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D186">
+        <v>4.3930000000000002E-3</v>
+      </c>
+      <c r="E186">
         <v>935</v>
       </c>
-      <c r="C189">
-        <v>0.474464</v>
-      </c>
-    </row>
-    <row r="190" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B190">
+    </row>
+    <row r="187" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D187">
+        <v>4.5360000000000001E-3</v>
+      </c>
+      <c r="E187">
         <v>940</v>
       </c>
-      <c r="C190">
-        <v>0.48125000000000001</v>
-      </c>
-    </row>
-    <row r="191" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B191">
+    </row>
+    <row r="188" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D188">
+        <v>4.3930000000000002E-3</v>
+      </c>
+      <c r="E188">
         <v>945</v>
       </c>
-      <c r="C191">
-        <v>0.49267899999999998</v>
-      </c>
-    </row>
-    <row r="192" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B192">
+    </row>
+    <row r="189" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D189">
+        <v>4.4289999999999998E-3</v>
+      </c>
+      <c r="E189">
         <v>950</v>
       </c>
-      <c r="C192">
-        <v>0.49807099999999999</v>
-      </c>
-    </row>
-    <row r="193" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B193">
+    </row>
+    <row r="190" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D190">
+        <v>4.5710000000000004E-3</v>
+      </c>
+      <c r="E190">
         <v>955</v>
       </c>
-      <c r="C193">
-        <v>0.50592899999999996</v>
-      </c>
-    </row>
-    <row r="194" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B194">
+    </row>
+    <row r="191" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D191">
+        <v>4.6430000000000004E-3</v>
+      </c>
+      <c r="E191">
         <v>960</v>
       </c>
-      <c r="C194">
-        <v>0.51324999999999998</v>
-      </c>
-    </row>
-    <row r="195" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B195">
+    </row>
+    <row r="192" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D192">
+        <v>4.7499999999999999E-3</v>
+      </c>
+      <c r="E192">
         <v>965</v>
       </c>
-      <c r="C195">
-        <v>0.52514300000000003</v>
-      </c>
-    </row>
-    <row r="196" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B196">
+    </row>
+    <row r="193" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D193">
+        <v>4.5710000000000004E-3</v>
+      </c>
+      <c r="E193">
         <v>970</v>
       </c>
-      <c r="C196">
-        <v>0.52964299999999997</v>
-      </c>
-    </row>
-    <row r="197" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B197">
+    </row>
+    <row r="194" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D194">
+        <v>4.7140000000000003E-3</v>
+      </c>
+      <c r="E194">
         <v>975</v>
       </c>
-      <c r="C197">
-        <v>0.53725000000000001</v>
-      </c>
-    </row>
-    <row r="198" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B198">
+    </row>
+    <row r="195" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D195">
+        <v>4.8929999999999998E-3</v>
+      </c>
+      <c r="E195">
         <v>980</v>
       </c>
-      <c r="C198">
-        <v>0.54900000000000004</v>
-      </c>
-    </row>
-    <row r="199" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B199">
+    </row>
+    <row r="196" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D196">
+        <v>4.8570000000000002E-3</v>
+      </c>
+      <c r="E196">
         <v>985</v>
       </c>
-      <c r="C199">
-        <v>0.553643</v>
-      </c>
-    </row>
-    <row r="200" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B200">
+    </row>
+    <row r="197" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D197">
+        <v>4.8570000000000002E-3</v>
+      </c>
+      <c r="E197">
         <v>990</v>
       </c>
-      <c r="C200">
-        <v>0.56271400000000005</v>
-      </c>
-    </row>
-    <row r="201" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B201">
+    </row>
+    <row r="198" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D198">
+        <v>4.8929999999999998E-3</v>
+      </c>
+      <c r="E198">
         <v>995</v>
       </c>
-      <c r="C201">
-        <v>0.57492900000000002</v>
-      </c>
-    </row>
-    <row r="202" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B202">
+    </row>
+    <row r="199" spans="4:5" x14ac:dyDescent="0.3">
+      <c r="D199">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E199">
         <v>1000</v>
-      </c>
-      <c r="C202">
-        <v>0.57892900000000003</v>
       </c>
     </row>
   </sheetData>
